--- a/InputData/indst/PIFURfE/Perc Indst Fuel Use Reduction for Elec.xlsx
+++ b/InputData/indst/PIFURfE/Perc Indst Fuel Use Reduction for Elec.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\indst\PIFURfE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\indst\PIFURfE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5907E955-550C-485B-AFA7-F963D806D78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A914897-6198-4BC4-8C8A-3ACA6E0D593F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,16 +18,17 @@
     <sheet name="Med-High Temp Heat" sheetId="5" r:id="rId3"/>
     <sheet name="Low Temp Heat" sheetId="6" r:id="rId4"/>
     <sheet name="Cooling" sheetId="11" r:id="rId5"/>
-    <sheet name="Efficiencies" sheetId="8" r:id="rId6"/>
-    <sheet name="Temperature Breakdown" sheetId="9" r:id="rId7"/>
-    <sheet name="References" sheetId="10" r:id="rId8"/>
-    <sheet name="Mapping" sheetId="12" r:id="rId9"/>
-    <sheet name="PIFURfE" sheetId="2" r:id="rId10"/>
+    <sheet name="Other" sheetId="13" r:id="rId6"/>
+    <sheet name="Efficiencies" sheetId="8" r:id="rId7"/>
+    <sheet name="Temperature Breakdown" sheetId="9" r:id="rId8"/>
+    <sheet name="References" sheetId="10" r:id="rId9"/>
+    <sheet name="Mapping" sheetId="12" r:id="rId10"/>
+    <sheet name="PIFURfE" sheetId="2" r:id="rId11"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId11"/>
     <externalReference r:id="rId12"/>
     <externalReference r:id="rId13"/>
+    <externalReference r:id="rId14"/>
   </externalReferences>
   <definedNames>
     <definedName name="base.year">#REF!</definedName>
@@ -124,6 +125,12 @@
     <definedName name="Print_Area_MI">#REF!</definedName>
     <definedName name="Reliability.scenario">#REF!</definedName>
     <definedName name="small_hydro.capacity">#REF!</definedName>
+    <definedName name="solver_eng" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="10" hidden="1">0</definedName>
+    <definedName name="solver_typ" localSheetId="10" hidden="1">1</definedName>
+    <definedName name="solver_val" localSheetId="10" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="10" hidden="1">3</definedName>
     <definedName name="target.year">#REF!</definedName>
     <definedName name="Unit.acre">#REF!</definedName>
     <definedName name="unit.bcm">#REF!</definedName>
@@ -213,7 +220,7 @@
     <definedName name="XV.c.scenario">#REF!</definedName>
     <definedName name="xvi.scenario.fuelsplit">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -315,7 +322,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9005" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9083" uniqueCount="549">
   <si>
     <t>Percentage Industry Fuel Use Reduction for Electricity</t>
   </si>
@@ -1771,6 +1778,224 @@
   <si>
     <t>average</t>
   </si>
+  <si>
+    <t>Diesel</t>
+  </si>
+  <si>
+    <t>Tractor</t>
+  </si>
+  <si>
+    <t>https://www.m-hikari.com/ams/ams-2014/ams-129-132-2014/frisoAMS129-132-2014-1.pdf</t>
+  </si>
+  <si>
+    <t>Brake Thermal Efficiency and BSFC of Diesel  Engines: Mathematical Modeling and Comparison  between Diesel Oil and Biodiesel Fueling</t>
+  </si>
+  <si>
+    <t>D. Friso</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <t>unkn.</t>
+  </si>
+  <si>
+    <t>η</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0168169916000041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-field fuel use and load states of agricultural field machinery </t>
+  </si>
+  <si>
+    <t>S. Pitla, J.D. Luck, J. Werner, N. Line, S.A. Shearer</t>
+  </si>
+  <si>
+    <t>Field operation</t>
+  </si>
+  <si>
+    <t>weighted average engine speed</t>
+  </si>
+  <si>
+    <t>NH3 application</t>
+  </si>
+  <si>
+    <t>Field cultivation</t>
+  </si>
+  <si>
+    <t>Corn planting</t>
+  </si>
+  <si>
+    <t>Tables 2-5</t>
+  </si>
+  <si>
+    <t>% of total field time</t>
+  </si>
+  <si>
+    <t>TS-I</t>
+  </si>
+  <si>
+    <t>TS-II</t>
+  </si>
+  <si>
+    <t>TS-III</t>
+  </si>
+  <si>
+    <t>weighted-average torque</t>
+  </si>
+  <si>
+    <t>weighted-average engine speed</t>
+  </si>
+  <si>
+    <t>weighted values</t>
+  </si>
+  <si>
+    <t>weighted average torque %</t>
+  </si>
+  <si>
+    <t>t (%)</t>
+  </si>
+  <si>
+    <t>w (s^-1)</t>
+  </si>
+  <si>
+    <t>torque on fig 2</t>
+  </si>
+  <si>
+    <t>speed on fig 2</t>
+  </si>
+  <si>
+    <t>nom P [kW]</t>
+  </si>
+  <si>
+    <t>nom w [rpm]</t>
+  </si>
+  <si>
+    <t>245/127</t>
+  </si>
+  <si>
+    <t>4WD / MFWD</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ref 19 // </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>open circles are added via post processing and represent the weighted</t>
+    </r>
+  </si>
+  <si>
+    <t>average load &amp; engine speeds from ref 20 scaled by nominal engine speeds</t>
+  </si>
+  <si>
+    <t>max t at speed</t>
+  </si>
+  <si>
+    <t>(from figure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electric </t>
+  </si>
+  <si>
+    <t>load (fig 16)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ref 21 // </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>open circles are added via post processing and represent the weighted</t>
+    </r>
+  </si>
+  <si>
+    <t>speed on fig 14</t>
+  </si>
+  <si>
+    <t>torque on fig 14</t>
+  </si>
+  <si>
+    <t>150 (overload)</t>
+  </si>
+  <si>
+    <t>charging adjusted</t>
+  </si>
+  <si>
+    <t>Case of Study of the Electrification of a Tractor: Electric Motor Performance Requirements and Design</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/1996-1073/13/9/2197</t>
+  </si>
+  <si>
+    <t>D. Troncon, L. Alberti</t>
+  </si>
+  <si>
+    <t>Incentives for electrifying agricultural tractors in India</t>
+  </si>
+  <si>
+    <t>https://theicct.org/publication/india-hvs-evs-incentives-elec-tractors-india-oct22/</t>
+  </si>
+  <si>
+    <t>Z. Shao, S. Anup</t>
+  </si>
+  <si>
+    <t>PM Electric Motor</t>
+  </si>
+  <si>
+    <t>Custom autonomous</t>
+  </si>
+  <si>
+    <t>https://pub.epsilon.slu.se/id/document/20368600</t>
+  </si>
+  <si>
+    <t>Cost analysis of autonomous battery electric field tractors in agriculture</t>
+  </si>
+  <si>
+    <t>O. Lagnelov et al.</t>
+  </si>
+  <si>
+    <t>https://www.davidpublisher.com/Public/uploads/Contribute/5ba1b8c2036b0.pdf</t>
+  </si>
+  <si>
+    <t>An Autonomous Electric Powered Tractor—Simulation of All Operations on a Swedish Dairy Farm</t>
+  </si>
+  <si>
+    <t>J. Engstrom and O. Lagnelov</t>
+  </si>
+  <si>
+    <t>Simulated autonomous</t>
+  </si>
+  <si>
+    <t>22,25</t>
+  </si>
+  <si>
+    <t>https://www.fueleconomy.gov/feg/atv-ev.shtml</t>
+  </si>
+  <si>
+    <t>Where the Energy Goes: Electric Cars</t>
+  </si>
+  <si>
+    <t>Ag tractors (mobile equipment)</t>
+  </si>
+  <si>
+    <t>Ref 20</t>
+  </si>
 </sst>
 </file>
 
@@ -1778,7 +2003,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -1861,7 +2086,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1895,6 +2120,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1964,7 +2195,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2133,6 +2364,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="5" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2148,9 +2391,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Body: normal cell" xfId="8" xr:uid="{D820F1CE-A112-4A27-BC46-BDF513CEFB00}"/>
@@ -2692,6 +2932,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2699,7 +2940,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:noFill/>
@@ -3364,6 +3604,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3371,7 +3612,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4720,6 +4960,99 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>216087</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>164826</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{088F89AB-CE5B-F0A1-4F45-076D0E594AB5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6387353" y="717176"/>
+          <a:ext cx="4448735" cy="2133887"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>122869</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>160057</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7884575-8411-5B0D-DD4E-256A7A187D4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6387353" y="3406588"/>
+          <a:ext cx="2546515" cy="2129118"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -5238,6 +5571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5461,8 +5795,881 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA4BAC4-DAD5-4B3C-8999-FA6866E1C28D}">
+  <sheetPr codeName="Sheet10"/>
+  <dimension ref="B1:J26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="11.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D1" s="66" t="s">
+        <v>314</v>
+      </c>
+      <c r="E1" s="66" t="s">
+        <v>316</v>
+      </c>
+      <c r="F1" s="66" t="s">
+        <v>317</v>
+      </c>
+      <c r="G1" s="66" t="s">
+        <v>318</v>
+      </c>
+      <c r="H1" s="66" t="s">
+        <v>320</v>
+      </c>
+      <c r="I1" s="66" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D2" s="6">
+        <f>IF($C2="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C2,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.22712128261679607</v>
+      </c>
+      <c r="E2" s="6">
+        <f>IF($C2="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C2,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.18096501818637736</v>
+      </c>
+      <c r="F2" s="6">
+        <f>IF($C2="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C2,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.20705409259653504</v>
+      </c>
+      <c r="G2" s="6">
+        <f>IF($C2="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C2,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>9.990108165832158E-2</v>
+      </c>
+      <c r="H2" s="6">
+        <f>IF($C2="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C2,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>6.4928393115227967E-2</v>
+      </c>
+      <c r="I2" s="6">
+        <f>IF($C2="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C2,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.22003013182674194</v>
+      </c>
+      <c r="J2" s="4"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C3" t="s">
+        <v>484</v>
+      </c>
+      <c r="D3" s="6">
+        <f>IF($C3="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C3,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.22712128261679607</v>
+      </c>
+      <c r="E3" s="6">
+        <f>IF($C3="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C3,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.18096501818637736</v>
+      </c>
+      <c r="F3" s="6">
+        <f>IF($C3="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C3,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.20705409259653504</v>
+      </c>
+      <c r="G3" s="6">
+        <f>IF($C3="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C3,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>9.990108165832158E-2</v>
+      </c>
+      <c r="H3" s="6">
+        <f>IF($C3="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C3,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>6.4928393115227967E-2</v>
+      </c>
+      <c r="I3" s="6">
+        <f>IF($C3="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C3,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.22003013182674194</v>
+      </c>
+      <c r="J3" s="4"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C4" t="s">
+        <v>356</v>
+      </c>
+      <c r="D4" s="6">
+        <f>IF($C4="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C4,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.03</v>
+      </c>
+      <c r="E4" s="6">
+        <f>IF($C4="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C4,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="F4" s="6">
+        <f>IF($C4="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C4,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.15</v>
+      </c>
+      <c r="G4" s="6">
+        <f>IF($C4="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C4,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.02</v>
+      </c>
+      <c r="H4" s="6">
+        <f>IF($C4="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C4,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.23</v>
+      </c>
+      <c r="I4" s="6">
+        <f>IF($C4="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C4,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="4"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>459</v>
+      </c>
+      <c r="C5" t="s">
+        <v>484</v>
+      </c>
+      <c r="D5" s="6">
+        <f>IF($C5="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C5,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.22712128261679607</v>
+      </c>
+      <c r="E5" s="6">
+        <f>IF($C5="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C5,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.18096501818637736</v>
+      </c>
+      <c r="F5" s="6">
+        <f>IF($C5="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C5,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.20705409259653504</v>
+      </c>
+      <c r="G5" s="6">
+        <f>IF($C5="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C5,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>9.990108165832158E-2</v>
+      </c>
+      <c r="H5" s="6">
+        <f>IF($C5="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C5,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>6.4928393115227967E-2</v>
+      </c>
+      <c r="I5" s="6">
+        <f>IF($C5="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C5,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.22003013182674194</v>
+      </c>
+      <c r="J5" s="4"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>460</v>
+      </c>
+      <c r="C6" t="s">
+        <v>361</v>
+      </c>
+      <c r="D6" s="6">
+        <f>IF($C6="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C6,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E6" s="6">
+        <f>IF($C6="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C6,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.43</v>
+      </c>
+      <c r="F6" s="6">
+        <f>IF($C6="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C6,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="6">
+        <f>IF($C6="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C6,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.02</v>
+      </c>
+      <c r="H6" s="6">
+        <f>IF($C6="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C6,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="6">
+        <f>IF($C6="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C6,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>461</v>
+      </c>
+      <c r="C7" t="s">
+        <v>362</v>
+      </c>
+      <c r="D7" s="6">
+        <f>IF($C7="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C7,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.37818181818181817</v>
+      </c>
+      <c r="E7" s="6">
+        <f>IF($C7="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C7,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.18242424242424241</v>
+      </c>
+      <c r="F7" s="6">
+        <f>IF($C7="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C7,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.26363636363636361</v>
+      </c>
+      <c r="G7" s="6">
+        <f>IF($C7="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C7,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.17575757575757572</v>
+      </c>
+      <c r="H7" s="6">
+        <f>IF($C7="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C7,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="6">
+        <f>IF($C7="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C7,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="4"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>462</v>
+      </c>
+      <c r="C8" t="s">
+        <v>363</v>
+      </c>
+      <c r="D8" s="6">
+        <f>IF($C8="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C8,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>9.4117647058823542E-2</v>
+      </c>
+      <c r="E8" s="6">
+        <f>IF($C8="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C8,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.17058823529411765</v>
+      </c>
+      <c r="F8" s="6">
+        <f>IF($C8="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C8,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.44117647058823534</v>
+      </c>
+      <c r="G8" s="6">
+        <f>IF($C8="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C8,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.29411764705882354</v>
+      </c>
+      <c r="H8" s="6">
+        <f>IF($C8="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C8,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="6">
+        <f>IF($C8="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C8,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="4"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>463</v>
+      </c>
+      <c r="C9" t="s">
+        <v>364</v>
+      </c>
+      <c r="D9" s="6">
+        <f>IF($C9="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C9,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.33</v>
+      </c>
+      <c r="E9" s="6">
+        <f>IF($C9="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C9,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.1</v>
+      </c>
+      <c r="F9" s="6">
+        <f>IF($C9="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C9,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.15</v>
+      </c>
+      <c r="G9" s="6">
+        <f>IF($C9="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C9,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
+        <f>IF($C9="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C9,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.42</v>
+      </c>
+      <c r="I9" s="6">
+        <f>IF($C9="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C9,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="4"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C10" t="s">
+        <v>365</v>
+      </c>
+      <c r="D10" s="6">
+        <f>IF($C10="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C10,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.08</v>
+      </c>
+      <c r="E10" s="6">
+        <f>IF($C10="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C10,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.18</v>
+      </c>
+      <c r="F10" s="6">
+        <f>IF($C10="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C10,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.46</v>
+      </c>
+      <c r="G10" s="6">
+        <f>IF($C10="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C10,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.27</v>
+      </c>
+      <c r="H10" s="6">
+        <f>IF($C10="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C10,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="6">
+        <f>IF($C10="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C10,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.01</v>
+      </c>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>465</v>
+      </c>
+      <c r="C11" t="s">
+        <v>356</v>
+      </c>
+      <c r="D11" s="6">
+        <f>IF($C11="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C11,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.03</v>
+      </c>
+      <c r="E11" s="6">
+        <f>IF($C11="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C11,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="F11" s="6">
+        <f>IF($C11="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C11,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.15</v>
+      </c>
+      <c r="G11" s="6">
+        <f>IF($C11="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C11,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.02</v>
+      </c>
+      <c r="H11" s="6">
+        <f>IF($C11="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C11,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.23</v>
+      </c>
+      <c r="I11" s="6">
+        <f>IF($C11="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C11,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>466</v>
+      </c>
+      <c r="C12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D12" s="6">
+        <f>IF($C12="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C12,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.04</v>
+      </c>
+      <c r="E12" s="6">
+        <f>IF($C12="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C12,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.38</v>
+      </c>
+      <c r="F12" s="6">
+        <f>IF($C12="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C12,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G12" s="6">
+        <f>IF($C12="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C12,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
+        <f>IF($C12="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C12,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="6">
+        <f>IF($C12="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C12,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>467</v>
+      </c>
+      <c r="C13" t="s">
+        <v>347</v>
+      </c>
+      <c r="D13" s="6">
+        <f>IF($C13="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C13,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <f>IF($C13="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C13,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <f>IF($C13="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C13,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <f>IF($C13="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C13,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>1.9230769230769232E-2</v>
+      </c>
+      <c r="H13" s="6">
+        <f>IF($C13="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C13,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>5.7692307692307696E-2</v>
+      </c>
+      <c r="I13" s="6">
+        <f>IF($C13="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C13,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.92307692307692302</v>
+      </c>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>468</v>
+      </c>
+      <c r="C14" t="s">
+        <v>367</v>
+      </c>
+      <c r="D14" s="6">
+        <f>IF($C14="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C14,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <f>IF($C14="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C14,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <f>IF($C14="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C14,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.16</v>
+      </c>
+      <c r="G14" s="6">
+        <f>IF($C14="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C14,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="6">
+        <f>IF($C14="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C14,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="6">
+        <f>IF($C14="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C14,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.84</v>
+      </c>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>469</v>
+      </c>
+      <c r="C15" t="s">
+        <v>368</v>
+      </c>
+      <c r="D15" s="6">
+        <f>IF($C15="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C15,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>4.5197740112994352E-3</v>
+      </c>
+      <c r="E15" s="6">
+        <f>IF($C15="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C15,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>3.0131826741996233E-3</v>
+      </c>
+      <c r="F15" s="6">
+        <f>IF($C15="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C15,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>5.6497175141242938E-3</v>
+      </c>
+      <c r="G15" s="6">
+        <f>IF($C15="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C15,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>9.4161958568738224E-3</v>
+      </c>
+      <c r="H15" s="6">
+        <f>IF($C15="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C15,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="I15" s="6">
+        <f>IF($C15="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C15,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.96045197740112986</v>
+      </c>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>470</v>
+      </c>
+      <c r="C16" t="s">
+        <v>369</v>
+      </c>
+      <c r="D16" s="6">
+        <f>IF($C16="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C16,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.3</v>
+      </c>
+      <c r="E16" s="6">
+        <f>IF($C16="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C16,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="6">
+        <f>IF($C16="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C16,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="6">
+        <f>IF($C16="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C16,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.06</v>
+      </c>
+      <c r="H16" s="6">
+        <f>IF($C16="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C16,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.15</v>
+      </c>
+      <c r="I16" s="6">
+        <f>IF($C16="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C16,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.49</v>
+      </c>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>471</v>
+      </c>
+      <c r="C17" t="s">
+        <v>374</v>
+      </c>
+      <c r="D17" s="6">
+        <f>IF($C17="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C17,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.33488372093023255</v>
+      </c>
+      <c r="E17" s="6">
+        <f>IF($C17="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C17,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.14961240310077517</v>
+      </c>
+      <c r="F17" s="6">
+        <f>IF($C17="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C17,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.19767441860465118</v>
+      </c>
+      <c r="G17" s="6">
+        <f>IF($C17="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C17,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.13178294573643412</v>
+      </c>
+      <c r="H17" s="6">
+        <f>IF($C17="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C17,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="6">
+        <f>IF($C17="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C17,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.18604651162790697</v>
+      </c>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>472</v>
+      </c>
+      <c r="C18" t="s">
+        <v>372</v>
+      </c>
+      <c r="D18" s="6">
+        <f>IF($C18="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C18,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.33488372093023255</v>
+      </c>
+      <c r="E18" s="6">
+        <f>IF($C18="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C18,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.14961240310077517</v>
+      </c>
+      <c r="F18" s="6">
+        <f>IF($C18="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C18,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.19767441860465118</v>
+      </c>
+      <c r="G18" s="6">
+        <f>IF($C18="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C18,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.13178294573643412</v>
+      </c>
+      <c r="H18" s="6">
+        <f>IF($C18="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C18,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="6">
+        <f>IF($C18="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C18,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.18604651162790697</v>
+      </c>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>473</v>
+      </c>
+      <c r="C19" t="s">
+        <v>370</v>
+      </c>
+      <c r="D19" s="6">
+        <f>IF($C19="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C19,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.26046511627906982</v>
+      </c>
+      <c r="E19" s="6">
+        <f>IF($C19="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C19,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.1</v>
+      </c>
+      <c r="F19" s="6">
+        <f>IF($C19="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C19,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.10465116279069767</v>
+      </c>
+      <c r="G19" s="6">
+        <f>IF($C19="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C19,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.12209302325581395</v>
+      </c>
+      <c r="H19" s="6">
+        <f>IF($C19="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C19,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.15697674418604651</v>
+      </c>
+      <c r="I19" s="6">
+        <f>IF($C19="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C19,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.2558139534883721</v>
+      </c>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>474</v>
+      </c>
+      <c r="C20" t="s">
+        <v>370</v>
+      </c>
+      <c r="D20" s="6">
+        <f>IF($C20="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C20,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.26046511627906982</v>
+      </c>
+      <c r="E20" s="6">
+        <f>IF($C20="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C20,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.1</v>
+      </c>
+      <c r="F20" s="6">
+        <f>IF($C20="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C20,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.10465116279069767</v>
+      </c>
+      <c r="G20" s="6">
+        <f>IF($C20="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C20,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.12209302325581395</v>
+      </c>
+      <c r="H20" s="6">
+        <f>IF($C20="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C20,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.15697674418604651</v>
+      </c>
+      <c r="I20" s="6">
+        <f>IF($C20="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C20,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.2558139534883721</v>
+      </c>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>475</v>
+      </c>
+      <c r="C21" t="s">
+        <v>371</v>
+      </c>
+      <c r="D21" s="6">
+        <f>IF($C21="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C21,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.33488372093023255</v>
+      </c>
+      <c r="E21" s="6">
+        <f>IF($C21="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C21,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.14961240310077517</v>
+      </c>
+      <c r="F21" s="6">
+        <f>IF($C21="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C21,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.19767441860465118</v>
+      </c>
+      <c r="G21" s="6">
+        <f>IF($C21="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C21,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.13178294573643412</v>
+      </c>
+      <c r="H21" s="6">
+        <f>IF($C21="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C21,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="6">
+        <f>IF($C21="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C21,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.18604651162790697</v>
+      </c>
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>476</v>
+      </c>
+      <c r="C22" t="s">
+        <v>371</v>
+      </c>
+      <c r="D22" s="6">
+        <f>IF($C22="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C22,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.33488372093023255</v>
+      </c>
+      <c r="E22" s="6">
+        <f>IF($C22="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C22,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.14961240310077517</v>
+      </c>
+      <c r="F22" s="6">
+        <f>IF($C22="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C22,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.19767441860465118</v>
+      </c>
+      <c r="G22" s="6">
+        <f>IF($C22="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C22,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.13178294573643412</v>
+      </c>
+      <c r="H22" s="6">
+        <f>IF($C22="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C22,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="6">
+        <f>IF($C22="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C22,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.18604651162790697</v>
+      </c>
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>477</v>
+      </c>
+      <c r="C23" t="s">
+        <v>375</v>
+      </c>
+      <c r="D23" s="6">
+        <f>IF($C23="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C23,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.33488372093023255</v>
+      </c>
+      <c r="E23" s="6">
+        <f>IF($C23="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C23,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.14961240310077517</v>
+      </c>
+      <c r="F23" s="6">
+        <f>IF($C23="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C23,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.19767441860465118</v>
+      </c>
+      <c r="G23" s="6">
+        <f>IF($C23="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C23,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.13178294573643412</v>
+      </c>
+      <c r="H23" s="6">
+        <f>IF($C23="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C23,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="6">
+        <f>IF($C23="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C23,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.18604651162790697</v>
+      </c>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>478</v>
+      </c>
+      <c r="C24" t="s">
+        <v>484</v>
+      </c>
+      <c r="D24" s="6">
+        <f>IF($C24="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C24,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.22712128261679607</v>
+      </c>
+      <c r="E24" s="6">
+        <f>IF($C24="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C24,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.18096501818637736</v>
+      </c>
+      <c r="F24" s="6">
+        <f>IF($C24="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C24,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.20705409259653504</v>
+      </c>
+      <c r="G24" s="6">
+        <f>IF($C24="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C24,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>9.990108165832158E-2</v>
+      </c>
+      <c r="H24" s="6">
+        <f>IF($C24="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C24,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>6.4928393115227967E-2</v>
+      </c>
+      <c r="I24" s="6">
+        <f>IF($C24="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C24,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.22003013182674194</v>
+      </c>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>479</v>
+      </c>
+      <c r="C25" t="s">
+        <v>484</v>
+      </c>
+      <c r="D25" s="6">
+        <f>IF($C25="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C25,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.22712128261679607</v>
+      </c>
+      <c r="E25" s="6">
+        <f>IF($C25="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C25,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.18096501818637736</v>
+      </c>
+      <c r="F25" s="6">
+        <f>IF($C25="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C25,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.20705409259653504</v>
+      </c>
+      <c r="G25" s="6">
+        <f>IF($C25="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C25,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>9.990108165832158E-2</v>
+      </c>
+      <c r="H25" s="6">
+        <f>IF($C25="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C25,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>6.4928393115227967E-2</v>
+      </c>
+      <c r="I25" s="6">
+        <f>IF($C25="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C25,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.22003013182674194</v>
+      </c>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>480</v>
+      </c>
+      <c r="C26" t="s">
+        <v>484</v>
+      </c>
+      <c r="D26" s="6">
+        <f>IF($C26="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C26,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.22712128261679607</v>
+      </c>
+      <c r="E26" s="6">
+        <f>IF($C26="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C26,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.18096501818637736</v>
+      </c>
+      <c r="F26" s="6">
+        <f>IF($C26="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C26,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.20705409259653504</v>
+      </c>
+      <c r="G26" s="6">
+        <f>IF($C26="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C26,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>9.990108165832158E-2</v>
+      </c>
+      <c r="H26" s="6">
+        <f>IF($C26="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C26,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>6.4928393115227967E-2</v>
+      </c>
+      <c r="I26" s="6">
+        <f>IF($C26="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C26,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
+        <v>0.22003013182674194</v>
+      </c>
+      <c r="J26" s="4"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:I26">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet11">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:I26"/>
@@ -5472,7 +6679,7 @@
     <col min="2" max="9" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>303</v>
       </c>
@@ -5505,110 +6712,110 @@
       <c r="A2" t="s">
         <v>456</v>
       </c>
-      <c r="B2" s="85">
+      <c r="B2" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D2:I2)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D2:I2),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.58424137438649415</v>
       </c>
-      <c r="C2" s="85">
+      <c r="C2" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D2:I2)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D2:I2),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.71523255596540547</v>
       </c>
-      <c r="D2" s="85">
+      <c r="D2" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D2:I2)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D2:I2),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.29055119036728594</v>
       </c>
-      <c r="E2" s="85">
+      <c r="E2" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D2:I2)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D2:I2),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.50307566278577831</v>
       </c>
-      <c r="F2" s="86">
+      <c r="F2" s="81">
         <f>Cooling!B15</f>
         <v>0.80536907536907543</v>
       </c>
-      <c r="G2" s="86">
+      <c r="G2" s="81">
         <f>Efficiencies!B25</f>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H2" s="87">
+      <c r="H2" s="81">
         <f>AVERAGE(C2:G2)</f>
         <v>0.5732623635641757</v>
       </c>
-      <c r="I2" s="87">
-        <f>H2</f>
-        <v>0.5732623635641757</v>
+      <c r="I2" s="85">
+        <f>Other!B15</f>
+        <v>0.57060049240377109</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>457</v>
       </c>
-      <c r="B3" s="85">
+      <c r="B3" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D3:I3)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D3:I3),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.58424137438649415</v>
       </c>
-      <c r="C3" s="85">
+      <c r="C3" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D3:I3)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D3:I3),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.71523255596540547</v>
       </c>
-      <c r="D3" s="85">
+      <c r="D3" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D3:I3)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D3:I3),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.29055119036728594</v>
       </c>
-      <c r="E3" s="85">
+      <c r="E3" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D3:I3)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D3:I3),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.50307566278577831</v>
       </c>
-      <c r="F3" s="86">
+      <c r="F3" s="81">
         <f>F2</f>
         <v>0.80536907536907543</v>
       </c>
-      <c r="G3" s="86">
+      <c r="G3" s="81">
         <f>G2</f>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H3" s="87">
+      <c r="H3" s="81">
         <f t="shared" ref="H3:H26" si="0">AVERAGE(C3:G3)</f>
         <v>0.5732623635641757</v>
       </c>
-      <c r="I3" s="87">
-        <f t="shared" ref="I3:I26" si="1">H3</f>
-        <v>0.5732623635641757</v>
+      <c r="I3" s="85">
+        <f>I2</f>
+        <v>0.57060049240377109</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>458</v>
       </c>
-      <c r="B4" s="85">
+      <c r="B4" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D4:I4)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D4:I4),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.59149898989898986</v>
       </c>
-      <c r="C4" s="85">
+      <c r="C4" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D4:I4)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D4:I4),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.6592559743779256</v>
       </c>
-      <c r="D4" s="85">
+      <c r="D4" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D4:I4)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D4:I4),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.28527512891149248</v>
       </c>
-      <c r="E4" s="85">
+      <c r="E4" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D4:I4)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D4:I4),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.48016779363886791</v>
       </c>
-      <c r="F4" s="86">
-        <f t="shared" ref="F4:F26" si="2">F3</f>
+      <c r="F4" s="81">
+        <f t="shared" ref="F4:F26" si="1">F3</f>
         <v>0.80536907536907543</v>
       </c>
-      <c r="G4" s="86">
-        <f t="shared" ref="G4:G26" si="3">G3</f>
+      <c r="G4" s="81">
+        <f t="shared" ref="G4:G26" si="2">G3</f>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H4" s="87">
+      <c r="H4" s="81">
         <f t="shared" si="0"/>
         <v>0.55643026112613903</v>
       </c>
-      <c r="I4" s="87">
-        <f t="shared" si="1"/>
+      <c r="I4" s="81">
+        <f t="shared" ref="I4:I25" si="3">H4</f>
         <v>0.55643026112613903</v>
       </c>
     </row>
@@ -5616,73 +6823,73 @@
       <c r="A5" t="s">
         <v>459</v>
       </c>
-      <c r="B5" s="85">
+      <c r="B5" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D5:I5)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D5:I5),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.58424137438649415</v>
       </c>
-      <c r="C5" s="85">
+      <c r="C5" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D5:I5)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D5:I5),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.71523255596540547</v>
       </c>
-      <c r="D5" s="85">
+      <c r="D5" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D5:I5)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D5:I5),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.29055119036728594</v>
       </c>
-      <c r="E5" s="85">
+      <c r="E5" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D5:I5)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D5:I5),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.50307566278577831</v>
       </c>
-      <c r="F5" s="86">
+      <c r="F5" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G5" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G5" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H5" s="87">
+      <c r="H5" s="81">
         <f t="shared" si="0"/>
         <v>0.5732623635641757</v>
       </c>
-      <c r="I5" s="87">
-        <f t="shared" si="1"/>
-        <v>0.5732623635641757</v>
+      <c r="I5" s="85">
+        <f>I2</f>
+        <v>0.57060049240377109</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>460</v>
       </c>
-      <c r="B6" s="85">
+      <c r="B6" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D6:I6)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D6:I6),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.73780369290573378</v>
       </c>
-      <c r="C6" s="85">
+      <c r="C6" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D6:I6)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D6:I6),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.73780369290573378</v>
       </c>
-      <c r="D6" s="85">
+      <c r="D6" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D6:I6)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D6:I6),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.32656565656565656</v>
       </c>
-      <c r="E6" s="85">
+      <c r="E6" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D6:I6)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D6:I6),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.32656565656565661</v>
       </c>
-      <c r="F6" s="86">
+      <c r="F6" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G6" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G6" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H6" s="87">
+      <c r="H6" s="81">
         <f t="shared" si="0"/>
         <v>0.54967748294789121</v>
       </c>
-      <c r="I6" s="87">
-        <f t="shared" si="1"/>
+      <c r="I6" s="81">
+        <f t="shared" si="3"/>
         <v>0.54967748294789121</v>
       </c>
     </row>
@@ -5690,36 +6897,36 @@
       <c r="A7" t="s">
         <v>461</v>
       </c>
-      <c r="B7" s="85">
+      <c r="B7" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D7:I7)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D7:I7),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.60270645530939648</v>
       </c>
-      <c r="C7" s="85">
+      <c r="C7" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D7:I7)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D7:I7),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.73201188073671308</v>
       </c>
-      <c r="D7" s="85">
+      <c r="D7" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D7:I7)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D7:I7),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.29282539682539677</v>
       </c>
-      <c r="E7" s="85">
+      <c r="E7" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D7:I7)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D7:I7),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.32656565656565656</v>
       </c>
-      <c r="F7" s="86">
+      <c r="F7" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G7" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G7" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H7" s="87">
+      <c r="H7" s="81">
         <f t="shared" si="0"/>
         <v>0.54177106856603507</v>
       </c>
-      <c r="I7" s="87">
-        <f t="shared" si="1"/>
+      <c r="I7" s="81">
+        <f t="shared" si="3"/>
         <v>0.54177106856603507</v>
       </c>
     </row>
@@ -5727,36 +6934,36 @@
       <c r="A8" t="s">
         <v>462</v>
       </c>
-      <c r="B8" s="85">
+      <c r="B8" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D8:I8)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D8:I8),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.44301370851370858</v>
       </c>
-      <c r="C8" s="85">
+      <c r="C8" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D8:I8)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D8:I8),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.6489663986806844</v>
       </c>
-      <c r="D8" s="85">
+      <c r="D8" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D8:I8)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D8:I8),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.29282539682539677</v>
       </c>
-      <c r="E8" s="85">
+      <c r="E8" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D8:I8)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D8:I8),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.32656565656565656</v>
       </c>
-      <c r="F8" s="86">
+      <c r="F8" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G8" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G8" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H8" s="87">
+      <c r="H8" s="81">
         <f t="shared" si="0"/>
         <v>0.5251619721548294</v>
       </c>
-      <c r="I8" s="87">
-        <f t="shared" si="1"/>
+      <c r="I8" s="81">
+        <f t="shared" si="3"/>
         <v>0.5251619721548294</v>
       </c>
     </row>
@@ -5764,36 +6971,36 @@
       <c r="A9" t="s">
         <v>463</v>
       </c>
-      <c r="B9" s="85">
+      <c r="B9" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D9:I9)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D9:I9),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.64081355426182995</v>
       </c>
-      <c r="C9" s="85">
+      <c r="C9" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D9:I9)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D9:I9),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.74941582761807468</v>
       </c>
-      <c r="D9" s="85">
+      <c r="D9" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D9:I9)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D9:I9),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.28282828282828276</v>
       </c>
-      <c r="E9" s="85">
+      <c r="E9" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D9:I9)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D9:I9),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.48818181818181811</v>
       </c>
-      <c r="F9" s="86">
+      <c r="F9" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G9" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G9" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H9" s="87">
+      <c r="H9" s="81">
         <f t="shared" si="0"/>
         <v>0.57557566746611688</v>
       </c>
-      <c r="I9" s="87">
-        <f t="shared" si="1"/>
+      <c r="I9" s="81">
+        <f t="shared" si="3"/>
         <v>0.57557566746611688</v>
       </c>
     </row>
@@ -5801,36 +7008,36 @@
       <c r="A10" t="s">
         <v>464</v>
       </c>
-      <c r="B10" s="85">
+      <c r="B10" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D10:I10)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D10:I10),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.43474346641013317</v>
       </c>
-      <c r="C10" s="85">
+      <c r="C10" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D10:I10)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D10:I10),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.64027577360910692</v>
       </c>
-      <c r="D10" s="85">
+      <c r="D10" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D10:I10)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D10:I10),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.29187739463601531</v>
       </c>
-      <c r="E10" s="85">
+      <c r="E10" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D10:I10)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D10:I10),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.33987902278599952</v>
       </c>
-      <c r="F10" s="86">
+      <c r="F10" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G10" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G10" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H10" s="87">
+      <c r="H10" s="81">
         <f t="shared" si="0"/>
         <v>0.52589691994670607</v>
       </c>
-      <c r="I10" s="87">
-        <f t="shared" si="1"/>
+      <c r="I10" s="81">
+        <f t="shared" si="3"/>
         <v>0.52589691994670607</v>
       </c>
     </row>
@@ -5838,36 +7045,36 @@
       <c r="A11" t="s">
         <v>465</v>
       </c>
-      <c r="B11" s="85">
+      <c r="B11" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D11:I11)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D11:I11),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.59149898989898986</v>
       </c>
-      <c r="C11" s="85">
+      <c r="C11" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D11:I11)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D11:I11),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.6592559743779256</v>
       </c>
-      <c r="D11" s="85">
+      <c r="D11" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D11:I11)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D11:I11),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.28527512891149248</v>
       </c>
-      <c r="E11" s="85">
+      <c r="E11" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D11:I11)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D11:I11),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.48016779363886791</v>
       </c>
-      <c r="F11" s="86">
+      <c r="F11" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G11" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G11" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H11" s="87">
+      <c r="H11" s="81">
         <f t="shared" si="0"/>
         <v>0.55643026112613903</v>
       </c>
-      <c r="I11" s="87">
-        <f t="shared" si="1"/>
+      <c r="I11" s="81">
+        <f t="shared" si="3"/>
         <v>0.55643026112613903</v>
       </c>
     </row>
@@ -5875,36 +7082,36 @@
       <c r="A12" t="s">
         <v>466</v>
       </c>
-      <c r="B12" s="85">
+      <c r="B12" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D12:I12)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D12:I12),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.44744992784992788</v>
       </c>
-      <c r="C12" s="85">
+      <c r="C12" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D12:I12)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D12:I12),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.6272250297354901</v>
       </c>
-      <c r="D12" s="85">
+      <c r="D12" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D12:I12)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D12:I12),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.28282828282828276</v>
       </c>
-      <c r="E12" s="85">
+      <c r="E12" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D12:I12)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D12:I12),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.50307566278577831</v>
       </c>
-      <c r="F12" s="86">
+      <c r="F12" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G12" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G12" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H12" s="87">
+      <c r="H12" s="81">
         <f t="shared" si="0"/>
         <v>0.55411627681039211</v>
       </c>
-      <c r="I12" s="87">
-        <f t="shared" si="1"/>
+      <c r="I12" s="81">
+        <f t="shared" si="3"/>
         <v>0.55411627681039211</v>
       </c>
     </row>
@@ -5912,36 +7119,36 @@
       <c r="A13" t="s">
         <v>467</v>
       </c>
-      <c r="B13" s="85">
+      <c r="B13" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D13:I13)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D13:I13),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.58424137438649415</v>
       </c>
-      <c r="C13" s="85">
+      <c r="C13" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D13:I13)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D13:I13),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.71523255596540547</v>
       </c>
-      <c r="D13" s="85">
+      <c r="D13" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D13:I13)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D13:I13),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.32656565656565656</v>
       </c>
-      <c r="E13" s="85">
+      <c r="E13" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D13:I13)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D13:I13),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.54897580455719985</v>
       </c>
-      <c r="F13" s="86">
+      <c r="F13" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G13" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G13" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H13" s="87">
+      <c r="H13" s="81">
         <f t="shared" si="0"/>
         <v>0.58964528515813419</v>
       </c>
-      <c r="I13" s="87">
-        <f t="shared" si="1"/>
+      <c r="I13" s="81">
+        <f t="shared" si="3"/>
         <v>0.58964528515813419</v>
       </c>
     </row>
@@ -5949,36 +7156,36 @@
       <c r="A14" t="s">
         <v>468</v>
       </c>
-      <c r="B14" s="85">
+      <c r="B14" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D14:I14)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D14:I14),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.28282828282828282</v>
       </c>
-      <c r="C14" s="85">
+      <c r="C14" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D14:I14)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D14:I14),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.28282828282828287</v>
       </c>
-      <c r="D14" s="85">
+      <c r="D14" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D14:I14)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D14:I14),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.28282828282828276</v>
       </c>
-      <c r="E14" s="85">
+      <c r="E14" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D14:I14)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D14:I14),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.55555555555555558</v>
       </c>
-      <c r="F14" s="86">
+      <c r="F14" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G14" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G14" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H14" s="87">
+      <c r="H14" s="81">
         <f t="shared" si="0"/>
         <v>0.49573290598290598</v>
       </c>
-      <c r="I14" s="87">
-        <f t="shared" si="1"/>
+      <c r="I14" s="81">
+        <f t="shared" si="3"/>
         <v>0.49573290598290598</v>
       </c>
     </row>
@@ -5986,36 +7193,36 @@
       <c r="A15" t="s">
         <v>469</v>
       </c>
-      <c r="B15" s="85">
+      <c r="B15" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D15:I15)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D15:I15),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.54581076066790346</v>
       </c>
-      <c r="C15" s="85">
+      <c r="C15" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D15:I15)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D15:I15),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.71093929326487459</v>
       </c>
-      <c r="D15" s="85">
+      <c r="D15" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D15:I15)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D15:I15),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.30143993122716517</v>
       </c>
-      <c r="E15" s="85">
+      <c r="E15" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D15:I15)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D15:I15),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.55307790549169866</v>
       </c>
-      <c r="F15" s="86">
+      <c r="F15" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G15" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G15" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H15" s="87">
+      <c r="H15" s="81">
         <f t="shared" si="0"/>
         <v>0.58458190773722951</v>
       </c>
-      <c r="I15" s="87">
-        <f t="shared" si="1"/>
+      <c r="I15" s="81">
+        <f t="shared" si="3"/>
         <v>0.58458190773722951</v>
       </c>
     </row>
@@ -6023,36 +7230,36 @@
       <c r="A16" t="s">
         <v>470</v>
       </c>
-      <c r="B16" s="85">
+      <c r="B16" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D16:I16)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D16:I16),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.79714285714285704</v>
       </c>
-      <c r="C16" s="85">
+      <c r="C16" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D16:I16)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D16:I16),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.79714285714285704</v>
       </c>
-      <c r="D16" s="85">
+      <c r="D16" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D16:I16)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D16:I16),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.3265656565656565</v>
       </c>
-      <c r="E16" s="85">
+      <c r="E16" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D16:I16)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D16:I16),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.52841103341103357</v>
       </c>
-      <c r="F16" s="86">
+      <c r="F16" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G16" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G16" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H16" s="87">
+      <c r="H16" s="81">
         <f t="shared" si="0"/>
         <v>0.60191439116439127</v>
       </c>
-      <c r="I16" s="87">
-        <f t="shared" si="1"/>
+      <c r="I16" s="81">
+        <f t="shared" si="3"/>
         <v>0.60191439116439127</v>
       </c>
     </row>
@@ -6060,36 +7267,36 @@
       <c r="A17" t="s">
         <v>471</v>
       </c>
-      <c r="B17" s="85">
+      <c r="B17" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D17:I17)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D17:I17),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.61844834710743801</v>
       </c>
-      <c r="C17" s="85">
+      <c r="C17" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D17:I17)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D17:I17),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.7368569631751799</v>
       </c>
-      <c r="D17" s="85">
+      <c r="D17" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D17:I17)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D17:I17),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.29282539682539682</v>
       </c>
-      <c r="E17" s="85">
+      <c r="E17" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D17:I17)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D17:I17),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.48726032252348045</v>
       </c>
-      <c r="F17" s="86">
+      <c r="F17" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G17" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G17" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H17" s="87">
+      <c r="H17" s="81">
         <f t="shared" si="0"/>
         <v>0.57487901824529319</v>
       </c>
-      <c r="I17" s="87">
-        <f t="shared" si="1"/>
+      <c r="I17" s="81">
+        <f t="shared" si="3"/>
         <v>0.57487901824529319</v>
       </c>
     </row>
@@ -6097,36 +7304,36 @@
       <c r="A18" t="s">
         <v>472</v>
       </c>
-      <c r="B18" s="85">
+      <c r="B18" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D18:I18)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D18:I18),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.61844834710743801</v>
       </c>
-      <c r="C18" s="85">
+      <c r="C18" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D18:I18)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D18:I18),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.7368569631751799</v>
       </c>
-      <c r="D18" s="85">
+      <c r="D18" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D18:I18)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D18:I18),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.29282539682539682</v>
       </c>
-      <c r="E18" s="85">
+      <c r="E18" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D18:I18)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D18:I18),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.48726032252348045</v>
       </c>
-      <c r="F18" s="86">
+      <c r="F18" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G18" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G18" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H18" s="87">
+      <c r="H18" s="81">
         <f t="shared" si="0"/>
         <v>0.57487901824529319</v>
       </c>
-      <c r="I18" s="87">
-        <f t="shared" si="1"/>
+      <c r="I18" s="81">
+        <f t="shared" si="3"/>
         <v>0.57487901824529319</v>
       </c>
     </row>
@@ -6134,36 +7341,36 @@
       <c r="A19" t="s">
         <v>473</v>
       </c>
-      <c r="B19" s="85">
+      <c r="B19" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D19:I19)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D19:I19),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.6523458874458874</v>
       </c>
-      <c r="C19" s="85">
+      <c r="C19" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D19:I19)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D19:I19),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.74617324159643905</v>
       </c>
-      <c r="D19" s="85">
+      <c r="D19" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D19:I19)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D19:I19),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.29776299581177629</v>
       </c>
-      <c r="E19" s="85">
+      <c r="E19" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D19:I19)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D19:I19),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.49928326325455513</v>
       </c>
-      <c r="F19" s="86">
+      <c r="F19" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G19" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G19" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H19" s="87">
+      <c r="H19" s="81">
         <f t="shared" si="0"/>
         <v>0.58013438187303579</v>
       </c>
-      <c r="I19" s="87">
-        <f t="shared" si="1"/>
+      <c r="I19" s="81">
+        <f t="shared" si="3"/>
         <v>0.58013438187303579</v>
       </c>
     </row>
@@ -6171,36 +7378,36 @@
       <c r="A20" t="s">
         <v>474</v>
       </c>
-      <c r="B20" s="85">
+      <c r="B20" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D20:I20)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D20:I20),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.6523458874458874</v>
       </c>
-      <c r="C20" s="85">
+      <c r="C20" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D20:I20)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D20:I20),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.74617324159643905</v>
       </c>
-      <c r="D20" s="85">
+      <c r="D20" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D20:I20)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D20:I20),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.29776299581177629</v>
       </c>
-      <c r="E20" s="85">
+      <c r="E20" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D20:I20)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D20:I20),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.49928326325455513</v>
       </c>
-      <c r="F20" s="86">
+      <c r="F20" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G20" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G20" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H20" s="87">
+      <c r="H20" s="81">
         <f t="shared" si="0"/>
         <v>0.58013438187303579</v>
       </c>
-      <c r="I20" s="87">
-        <f t="shared" si="1"/>
+      <c r="I20" s="81">
+        <f t="shared" si="3"/>
         <v>0.58013438187303579</v>
       </c>
     </row>
@@ -6208,36 +7415,36 @@
       <c r="A21" t="s">
         <v>475</v>
       </c>
-      <c r="B21" s="85">
+      <c r="B21" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D21:I21)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D21:I21),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.61844834710743801</v>
       </c>
-      <c r="C21" s="85">
+      <c r="C21" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D21:I21)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D21:I21),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.7368569631751799</v>
       </c>
-      <c r="D21" s="85">
+      <c r="D21" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D21:I21)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D21:I21),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.29282539682539682</v>
       </c>
-      <c r="E21" s="85">
+      <c r="E21" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D21:I21)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D21:I21),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.48726032252348045</v>
       </c>
-      <c r="F21" s="86">
+      <c r="F21" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G21" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G21" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H21" s="87">
+      <c r="H21" s="81">
         <f t="shared" si="0"/>
         <v>0.57487901824529319</v>
       </c>
-      <c r="I21" s="87">
-        <f t="shared" si="1"/>
+      <c r="I21" s="81">
+        <f t="shared" si="3"/>
         <v>0.57487901824529319</v>
       </c>
     </row>
@@ -6245,36 +7452,36 @@
       <c r="A22" t="s">
         <v>476</v>
       </c>
-      <c r="B22" s="85">
+      <c r="B22" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D22:I22)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D22:I22),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.61844834710743801</v>
       </c>
-      <c r="C22" s="85">
+      <c r="C22" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D22:I22)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D22:I22),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.7368569631751799</v>
       </c>
-      <c r="D22" s="85">
+      <c r="D22" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D22:I22)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D22:I22),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.29282539682539682</v>
       </c>
-      <c r="E22" s="85">
+      <c r="E22" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D22:I22)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D22:I22),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.48726032252348045</v>
       </c>
-      <c r="F22" s="86">
+      <c r="F22" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G22" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G22" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H22" s="87">
+      <c r="H22" s="81">
         <f t="shared" si="0"/>
         <v>0.57487901824529319</v>
       </c>
-      <c r="I22" s="87">
-        <f t="shared" si="1"/>
+      <c r="I22" s="81">
+        <f t="shared" si="3"/>
         <v>0.57487901824529319</v>
       </c>
     </row>
@@ -6282,36 +7489,36 @@
       <c r="A23" t="s">
         <v>477</v>
       </c>
-      <c r="B23" s="85">
+      <c r="B23" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D23:I23)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D23:I23),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.61844834710743801</v>
       </c>
-      <c r="C23" s="85">
+      <c r="C23" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D23:I23)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D23:I23),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.7368569631751799</v>
       </c>
-      <c r="D23" s="85">
+      <c r="D23" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D23:I23)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D23:I23),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.29282539682539682</v>
       </c>
-      <c r="E23" s="85">
+      <c r="E23" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D23:I23)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D23:I23),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.48726032252348045</v>
       </c>
-      <c r="F23" s="86">
+      <c r="F23" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G23" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G23" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H23" s="87">
+      <c r="H23" s="81">
         <f t="shared" si="0"/>
         <v>0.57487901824529319</v>
       </c>
-      <c r="I23" s="87">
-        <f t="shared" si="1"/>
+      <c r="I23" s="81">
+        <f t="shared" si="3"/>
         <v>0.57487901824529319</v>
       </c>
     </row>
@@ -6319,36 +7526,36 @@
       <c r="A24" t="s">
         <v>478</v>
       </c>
-      <c r="B24" s="85">
+      <c r="B24" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D24:I24)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D24:I24),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.58424137438649415</v>
       </c>
-      <c r="C24" s="85">
+      <c r="C24" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D24:I24)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D24:I24),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.71523255596540547</v>
       </c>
-      <c r="D24" s="85">
+      <c r="D24" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D24:I24)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D24:I24),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.29055119036728594</v>
       </c>
-      <c r="E24" s="85">
+      <c r="E24" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D24:I24)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D24:I24),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.50307566278577831</v>
       </c>
-      <c r="F24" s="86">
+      <c r="F24" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G24" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G24" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H24" s="87">
+      <c r="H24" s="81">
         <f t="shared" si="0"/>
         <v>0.5732623635641757</v>
       </c>
-      <c r="I24" s="87">
-        <f t="shared" si="1"/>
+      <c r="I24" s="81">
+        <f t="shared" si="3"/>
         <v>0.5732623635641757</v>
       </c>
     </row>
@@ -6356,36 +7563,36 @@
       <c r="A25" t="s">
         <v>479</v>
       </c>
-      <c r="B25" s="85">
+      <c r="B25" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D25:I25)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D25:I25),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.58424137438649415</v>
       </c>
-      <c r="C25" s="85">
+      <c r="C25" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D25:I25)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D25:I25),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.71523255596540547</v>
       </c>
-      <c r="D25" s="85">
+      <c r="D25" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D25:I25)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D25:I25),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.29055119036728594</v>
       </c>
-      <c r="E25" s="85">
+      <c r="E25" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D25:I25)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D25:I25),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.50307566278577831</v>
       </c>
-      <c r="F25" s="86">
+      <c r="F25" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G25" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G25" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H25" s="87">
+      <c r="H25" s="81">
         <f t="shared" si="0"/>
         <v>0.5732623635641757</v>
       </c>
-      <c r="I25" s="87">
-        <f t="shared" si="1"/>
+      <c r="I25" s="81">
+        <f t="shared" si="3"/>
         <v>0.5732623635641757</v>
       </c>
     </row>
@@ -6393,37 +7600,37 @@
       <c r="A26" t="s">
         <v>480</v>
       </c>
-      <c r="B26" s="85">
+      <c r="B26" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D26:I26)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D26:I26),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
         <v>0.58424137438649415</v>
       </c>
-      <c r="C26" s="85">
+      <c r="C26" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Mapping!D26:I26)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Mapping!D26:I26),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$30:$H$30,Efficiencies!$C$27:$H$27))</f>
         <v>0.71523255596540547</v>
       </c>
-      <c r="D26" s="85">
+      <c r="D26" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Mapping!D26:I26)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Mapping!D26:I26),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$31:$H$31,Efficiencies!$C$27:$H$27))</f>
         <v>0.29055119036728594</v>
       </c>
-      <c r="E26" s="85">
+      <c r="E26" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Mapping!D26:I26)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Mapping!D26:I26),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$32:$H$32,Efficiencies!$C$27:$H$27))</f>
         <v>0.50307566278577831</v>
       </c>
-      <c r="F26" s="86">
+      <c r="F26" s="81">
+        <f t="shared" si="1"/>
+        <v>0.80536907536907543</v>
+      </c>
+      <c r="G26" s="81">
         <f t="shared" si="2"/>
-        <v>0.80536907536907543</v>
-      </c>
-      <c r="G26" s="86">
-        <f t="shared" si="3"/>
         <v>0.55208333333333337</v>
       </c>
-      <c r="H26" s="87">
+      <c r="H26" s="81">
         <f t="shared" si="0"/>
         <v>0.5732623635641757</v>
       </c>
-      <c r="I26" s="87">
-        <f t="shared" si="1"/>
-        <v>0.5732623635641757</v>
+      <c r="I26" s="85">
+        <f>I2</f>
+        <v>0.57060049240377109</v>
       </c>
     </row>
   </sheetData>
@@ -6458,7 +7665,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C717789-3B30-474B-99AA-384D29FECE60}">
-  <sheetPr>
+  <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L1880"/>
@@ -55815,296 +57022,296 @@
       </c>
     </row>
     <row r="1841" spans="1:12" s="52" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1841" s="82"/>
-      <c r="B1841" s="82"/>
-      <c r="C1841" s="82"/>
-      <c r="D1841" s="82"/>
-      <c r="E1841" s="82"/>
-      <c r="F1841" s="82"/>
-      <c r="G1841" s="82"/>
-      <c r="H1841" s="82"/>
-      <c r="I1841" s="82"/>
-      <c r="J1841" s="82"/>
+      <c r="A1841" s="90"/>
+      <c r="B1841" s="90"/>
+      <c r="C1841" s="90"/>
+      <c r="D1841" s="90"/>
+      <c r="E1841" s="90"/>
+      <c r="F1841" s="90"/>
+      <c r="G1841" s="90"/>
+      <c r="H1841" s="90"/>
+      <c r="I1841" s="90"/>
+      <c r="J1841" s="90"/>
       <c r="K1841" s="50"/>
       <c r="L1841" s="51"/>
     </row>
     <row r="1842" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1842" s="83"/>
-      <c r="B1842" s="83"/>
-      <c r="C1842" s="83"/>
-      <c r="D1842" s="83"/>
-      <c r="E1842" s="83"/>
-      <c r="F1842" s="83"/>
-      <c r="G1842" s="83"/>
-      <c r="H1842" s="83"/>
-      <c r="I1842" s="83"/>
-      <c r="J1842" s="83"/>
+      <c r="A1842" s="91"/>
+      <c r="B1842" s="91"/>
+      <c r="C1842" s="91"/>
+      <c r="D1842" s="91"/>
+      <c r="E1842" s="91"/>
+      <c r="F1842" s="91"/>
+      <c r="G1842" s="91"/>
+      <c r="H1842" s="91"/>
+      <c r="I1842" s="91"/>
+      <c r="J1842" s="91"/>
       <c r="K1842" s="53"/>
       <c r="L1842" s="54"/>
     </row>
     <row r="1843" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1843" s="83"/>
-      <c r="B1843" s="83"/>
-      <c r="C1843" s="83"/>
-      <c r="D1843" s="83"/>
-      <c r="E1843" s="83"/>
-      <c r="F1843" s="83"/>
-      <c r="G1843" s="83"/>
-      <c r="H1843" s="83"/>
-      <c r="I1843" s="83"/>
-      <c r="J1843" s="83"/>
+      <c r="A1843" s="91"/>
+      <c r="B1843" s="91"/>
+      <c r="C1843" s="91"/>
+      <c r="D1843" s="91"/>
+      <c r="E1843" s="91"/>
+      <c r="F1843" s="91"/>
+      <c r="G1843" s="91"/>
+      <c r="H1843" s="91"/>
+      <c r="I1843" s="91"/>
+      <c r="J1843" s="91"/>
       <c r="K1843" s="53"/>
       <c r="L1843" s="54"/>
     </row>
     <row r="1844" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1844" s="81"/>
-      <c r="B1844" s="81"/>
-      <c r="C1844" s="81"/>
-      <c r="D1844" s="81"/>
-      <c r="E1844" s="81"/>
-      <c r="F1844" s="81"/>
-      <c r="G1844" s="81"/>
-      <c r="H1844" s="81"/>
-      <c r="I1844" s="81"/>
-      <c r="J1844" s="81"/>
+      <c r="A1844" s="89"/>
+      <c r="B1844" s="89"/>
+      <c r="C1844" s="89"/>
+      <c r="D1844" s="89"/>
+      <c r="E1844" s="89"/>
+      <c r="F1844" s="89"/>
+      <c r="G1844" s="89"/>
+      <c r="H1844" s="89"/>
+      <c r="I1844" s="89"/>
+      <c r="J1844" s="89"/>
       <c r="K1844" s="55"/>
       <c r="L1844" s="54"/>
     </row>
     <row r="1845" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1845" s="81"/>
-      <c r="B1845" s="81"/>
-      <c r="C1845" s="81"/>
-      <c r="D1845" s="81"/>
-      <c r="E1845" s="81"/>
-      <c r="F1845" s="81"/>
-      <c r="G1845" s="81"/>
-      <c r="H1845" s="81"/>
-      <c r="I1845" s="81"/>
-      <c r="J1845" s="81"/>
+      <c r="A1845" s="89"/>
+      <c r="B1845" s="89"/>
+      <c r="C1845" s="89"/>
+      <c r="D1845" s="89"/>
+      <c r="E1845" s="89"/>
+      <c r="F1845" s="89"/>
+      <c r="G1845" s="89"/>
+      <c r="H1845" s="89"/>
+      <c r="I1845" s="89"/>
+      <c r="J1845" s="89"/>
       <c r="K1845" s="55"/>
       <c r="L1845" s="54"/>
     </row>
     <row r="1846" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1846" s="81"/>
-      <c r="B1846" s="81"/>
-      <c r="C1846" s="81"/>
-      <c r="D1846" s="81"/>
-      <c r="E1846" s="81"/>
-      <c r="F1846" s="81"/>
-      <c r="G1846" s="81"/>
-      <c r="H1846" s="81"/>
-      <c r="I1846" s="81"/>
-      <c r="J1846" s="81"/>
+      <c r="A1846" s="89"/>
+      <c r="B1846" s="89"/>
+      <c r="C1846" s="89"/>
+      <c r="D1846" s="89"/>
+      <c r="E1846" s="89"/>
+      <c r="F1846" s="89"/>
+      <c r="G1846" s="89"/>
+      <c r="H1846" s="89"/>
+      <c r="I1846" s="89"/>
+      <c r="J1846" s="89"/>
       <c r="K1846" s="55"/>
       <c r="L1846" s="54"/>
     </row>
     <row r="1847" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1847" s="81"/>
-      <c r="B1847" s="81"/>
-      <c r="C1847" s="81"/>
-      <c r="D1847" s="81"/>
-      <c r="E1847" s="81"/>
-      <c r="F1847" s="81"/>
-      <c r="G1847" s="81"/>
-      <c r="H1847" s="81"/>
-      <c r="I1847" s="81"/>
-      <c r="J1847" s="81"/>
+      <c r="A1847" s="89"/>
+      <c r="B1847" s="89"/>
+      <c r="C1847" s="89"/>
+      <c r="D1847" s="89"/>
+      <c r="E1847" s="89"/>
+      <c r="F1847" s="89"/>
+      <c r="G1847" s="89"/>
+      <c r="H1847" s="89"/>
+      <c r="I1847" s="89"/>
+      <c r="J1847" s="89"/>
       <c r="K1847" s="55"/>
       <c r="L1847" s="54"/>
     </row>
     <row r="1848" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1848" s="80"/>
-      <c r="B1848" s="80"/>
-      <c r="C1848" s="80"/>
-      <c r="D1848" s="80"/>
-      <c r="E1848" s="80"/>
-      <c r="F1848" s="80"/>
-      <c r="G1848" s="80"/>
-      <c r="H1848" s="80"/>
-      <c r="I1848" s="80"/>
-      <c r="J1848" s="80"/>
+      <c r="A1848" s="88"/>
+      <c r="B1848" s="88"/>
+      <c r="C1848" s="88"/>
+      <c r="D1848" s="88"/>
+      <c r="E1848" s="88"/>
+      <c r="F1848" s="88"/>
+      <c r="G1848" s="88"/>
+      <c r="H1848" s="88"/>
+      <c r="I1848" s="88"/>
+      <c r="J1848" s="88"/>
       <c r="K1848" s="54"/>
       <c r="L1848" s="54"/>
     </row>
     <row r="1849" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1849" s="80"/>
-      <c r="B1849" s="80"/>
-      <c r="C1849" s="80"/>
-      <c r="D1849" s="80"/>
-      <c r="E1849" s="80"/>
-      <c r="F1849" s="80"/>
-      <c r="G1849" s="80"/>
-      <c r="H1849" s="80"/>
-      <c r="I1849" s="80"/>
-      <c r="J1849" s="80"/>
+      <c r="A1849" s="88"/>
+      <c r="B1849" s="88"/>
+      <c r="C1849" s="88"/>
+      <c r="D1849" s="88"/>
+      <c r="E1849" s="88"/>
+      <c r="F1849" s="88"/>
+      <c r="G1849" s="88"/>
+      <c r="H1849" s="88"/>
+      <c r="I1849" s="88"/>
+      <c r="J1849" s="88"/>
       <c r="K1849" s="54"/>
       <c r="L1849" s="54"/>
     </row>
     <row r="1850" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1850" s="81"/>
-      <c r="B1850" s="81"/>
-      <c r="C1850" s="81"/>
-      <c r="D1850" s="81"/>
-      <c r="E1850" s="81"/>
-      <c r="F1850" s="81"/>
-      <c r="G1850" s="81"/>
-      <c r="H1850" s="81"/>
-      <c r="I1850" s="81"/>
-      <c r="J1850" s="81"/>
+      <c r="A1850" s="89"/>
+      <c r="B1850" s="89"/>
+      <c r="C1850" s="89"/>
+      <c r="D1850" s="89"/>
+      <c r="E1850" s="89"/>
+      <c r="F1850" s="89"/>
+      <c r="G1850" s="89"/>
+      <c r="H1850" s="89"/>
+      <c r="I1850" s="89"/>
+      <c r="J1850" s="89"/>
       <c r="K1850" s="55"/>
       <c r="L1850" s="54"/>
     </row>
     <row r="1851" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1851" s="81"/>
-      <c r="B1851" s="81"/>
-      <c r="C1851" s="81"/>
-      <c r="D1851" s="81"/>
-      <c r="E1851" s="81"/>
-      <c r="F1851" s="81"/>
-      <c r="G1851" s="81"/>
-      <c r="H1851" s="81"/>
-      <c r="I1851" s="81"/>
-      <c r="J1851" s="81"/>
+      <c r="A1851" s="89"/>
+      <c r="B1851" s="89"/>
+      <c r="C1851" s="89"/>
+      <c r="D1851" s="89"/>
+      <c r="E1851" s="89"/>
+      <c r="F1851" s="89"/>
+      <c r="G1851" s="89"/>
+      <c r="H1851" s="89"/>
+      <c r="I1851" s="89"/>
+      <c r="J1851" s="89"/>
       <c r="K1851" s="55"/>
       <c r="L1851" s="54"/>
     </row>
     <row r="1852" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1852" s="81"/>
-      <c r="B1852" s="81"/>
-      <c r="C1852" s="81"/>
-      <c r="D1852" s="81"/>
-      <c r="E1852" s="81"/>
-      <c r="F1852" s="81"/>
-      <c r="G1852" s="81"/>
-      <c r="H1852" s="81"/>
-      <c r="I1852" s="81"/>
-      <c r="J1852" s="81"/>
+      <c r="A1852" s="89"/>
+      <c r="B1852" s="89"/>
+      <c r="C1852" s="89"/>
+      <c r="D1852" s="89"/>
+      <c r="E1852" s="89"/>
+      <c r="F1852" s="89"/>
+      <c r="G1852" s="89"/>
+      <c r="H1852" s="89"/>
+      <c r="I1852" s="89"/>
+      <c r="J1852" s="89"/>
       <c r="K1852" s="55"/>
       <c r="L1852" s="54"/>
     </row>
     <row r="1853" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1853" s="81"/>
-      <c r="B1853" s="81"/>
-      <c r="C1853" s="81"/>
-      <c r="D1853" s="81"/>
-      <c r="E1853" s="81"/>
-      <c r="F1853" s="81"/>
-      <c r="G1853" s="81"/>
-      <c r="H1853" s="81"/>
-      <c r="I1853" s="81"/>
-      <c r="J1853" s="81"/>
+      <c r="A1853" s="89"/>
+      <c r="B1853" s="89"/>
+      <c r="C1853" s="89"/>
+      <c r="D1853" s="89"/>
+      <c r="E1853" s="89"/>
+      <c r="F1853" s="89"/>
+      <c r="G1853" s="89"/>
+      <c r="H1853" s="89"/>
+      <c r="I1853" s="89"/>
+      <c r="J1853" s="89"/>
       <c r="K1853" s="55"/>
       <c r="L1853" s="54"/>
     </row>
     <row r="1854" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1854" s="81"/>
-      <c r="B1854" s="81"/>
-      <c r="C1854" s="81"/>
-      <c r="D1854" s="81"/>
-      <c r="E1854" s="81"/>
-      <c r="F1854" s="81"/>
-      <c r="G1854" s="81"/>
-      <c r="H1854" s="81"/>
-      <c r="I1854" s="81"/>
-      <c r="J1854" s="81"/>
+      <c r="A1854" s="89"/>
+      <c r="B1854" s="89"/>
+      <c r="C1854" s="89"/>
+      <c r="D1854" s="89"/>
+      <c r="E1854" s="89"/>
+      <c r="F1854" s="89"/>
+      <c r="G1854" s="89"/>
+      <c r="H1854" s="89"/>
+      <c r="I1854" s="89"/>
+      <c r="J1854" s="89"/>
       <c r="K1854" s="55"/>
       <c r="L1854" s="54"/>
     </row>
     <row r="1855" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1855" s="81"/>
-      <c r="B1855" s="81"/>
-      <c r="C1855" s="81"/>
-      <c r="D1855" s="81"/>
-      <c r="E1855" s="81"/>
-      <c r="F1855" s="81"/>
-      <c r="G1855" s="81"/>
-      <c r="H1855" s="81"/>
-      <c r="I1855" s="81"/>
-      <c r="J1855" s="81"/>
+      <c r="A1855" s="89"/>
+      <c r="B1855" s="89"/>
+      <c r="C1855" s="89"/>
+      <c r="D1855" s="89"/>
+      <c r="E1855" s="89"/>
+      <c r="F1855" s="89"/>
+      <c r="G1855" s="89"/>
+      <c r="H1855" s="89"/>
+      <c r="I1855" s="89"/>
+      <c r="J1855" s="89"/>
       <c r="K1855" s="55"/>
       <c r="L1855" s="54"/>
     </row>
     <row r="1856" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1856" s="80"/>
-      <c r="B1856" s="80"/>
-      <c r="C1856" s="80"/>
-      <c r="D1856" s="80"/>
-      <c r="E1856" s="80"/>
-      <c r="F1856" s="80"/>
-      <c r="G1856" s="80"/>
-      <c r="H1856" s="80"/>
-      <c r="I1856" s="80"/>
-      <c r="J1856" s="80"/>
+      <c r="A1856" s="88"/>
+      <c r="B1856" s="88"/>
+      <c r="C1856" s="88"/>
+      <c r="D1856" s="88"/>
+      <c r="E1856" s="88"/>
+      <c r="F1856" s="88"/>
+      <c r="G1856" s="88"/>
+      <c r="H1856" s="88"/>
+      <c r="I1856" s="88"/>
+      <c r="J1856" s="88"/>
       <c r="K1856" s="54"/>
       <c r="L1856" s="54"/>
     </row>
     <row r="1857" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1857" s="80"/>
-      <c r="B1857" s="80"/>
-      <c r="C1857" s="80"/>
-      <c r="D1857" s="80"/>
-      <c r="E1857" s="80"/>
-      <c r="F1857" s="80"/>
-      <c r="G1857" s="80"/>
-      <c r="H1857" s="80"/>
-      <c r="I1857" s="80"/>
-      <c r="J1857" s="80"/>
+      <c r="A1857" s="88"/>
+      <c r="B1857" s="88"/>
+      <c r="C1857" s="88"/>
+      <c r="D1857" s="88"/>
+      <c r="E1857" s="88"/>
+      <c r="F1857" s="88"/>
+      <c r="G1857" s="88"/>
+      <c r="H1857" s="88"/>
+      <c r="I1857" s="88"/>
+      <c r="J1857" s="88"/>
       <c r="K1857" s="54"/>
       <c r="L1857" s="54"/>
     </row>
     <row r="1858" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1858" s="80"/>
-      <c r="B1858" s="80"/>
-      <c r="C1858" s="80"/>
-      <c r="D1858" s="80"/>
-      <c r="E1858" s="80"/>
-      <c r="F1858" s="80"/>
-      <c r="G1858" s="80"/>
-      <c r="H1858" s="80"/>
-      <c r="I1858" s="80"/>
-      <c r="J1858" s="80"/>
+      <c r="A1858" s="88"/>
+      <c r="B1858" s="88"/>
+      <c r="C1858" s="88"/>
+      <c r="D1858" s="88"/>
+      <c r="E1858" s="88"/>
+      <c r="F1858" s="88"/>
+      <c r="G1858" s="88"/>
+      <c r="H1858" s="88"/>
+      <c r="I1858" s="88"/>
+      <c r="J1858" s="88"/>
       <c r="K1858" s="54"/>
       <c r="L1858" s="54"/>
     </row>
     <row r="1859" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1859" s="80"/>
-      <c r="B1859" s="80"/>
-      <c r="C1859" s="80"/>
-      <c r="D1859" s="80"/>
-      <c r="E1859" s="80"/>
-      <c r="F1859" s="80"/>
-      <c r="G1859" s="80"/>
-      <c r="H1859" s="80"/>
-      <c r="I1859" s="80"/>
-      <c r="J1859" s="80"/>
+      <c r="A1859" s="88"/>
+      <c r="B1859" s="88"/>
+      <c r="C1859" s="88"/>
+      <c r="D1859" s="88"/>
+      <c r="E1859" s="88"/>
+      <c r="F1859" s="88"/>
+      <c r="G1859" s="88"/>
+      <c r="H1859" s="88"/>
+      <c r="I1859" s="88"/>
+      <c r="J1859" s="88"/>
       <c r="K1859" s="54"/>
       <c r="L1859" s="54"/>
     </row>
     <row r="1860" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1860" s="81"/>
-      <c r="B1860" s="81"/>
-      <c r="C1860" s="81"/>
-      <c r="D1860" s="81"/>
-      <c r="E1860" s="81"/>
-      <c r="F1860" s="81"/>
-      <c r="G1860" s="81"/>
-      <c r="H1860" s="81"/>
-      <c r="I1860" s="81"/>
-      <c r="J1860" s="81"/>
+      <c r="A1860" s="89"/>
+      <c r="B1860" s="89"/>
+      <c r="C1860" s="89"/>
+      <c r="D1860" s="89"/>
+      <c r="E1860" s="89"/>
+      <c r="F1860" s="89"/>
+      <c r="G1860" s="89"/>
+      <c r="H1860" s="89"/>
+      <c r="I1860" s="89"/>
+      <c r="J1860" s="89"/>
       <c r="K1860" s="55"/>
       <c r="L1860" s="54"/>
     </row>
     <row r="1861" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1861" s="80"/>
-      <c r="B1861" s="80"/>
-      <c r="C1861" s="80"/>
-      <c r="D1861" s="80"/>
-      <c r="E1861" s="80"/>
-      <c r="F1861" s="80"/>
-      <c r="G1861" s="80"/>
-      <c r="H1861" s="80"/>
-      <c r="I1861" s="80"/>
-      <c r="J1861" s="80"/>
+      <c r="A1861" s="88"/>
+      <c r="B1861" s="88"/>
+      <c r="C1861" s="88"/>
+      <c r="D1861" s="88"/>
+      <c r="E1861" s="88"/>
+      <c r="F1861" s="88"/>
+      <c r="G1861" s="88"/>
+      <c r="H1861" s="88"/>
+      <c r="I1861" s="88"/>
+      <c r="J1861" s="88"/>
       <c r="K1861" s="54"/>
     </row>
     <row r="1862" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
@@ -56238,6 +57445,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -56446,6 +57654,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E954BD9-F2E9-49BD-A674-73E808A9938A}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:J122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -57143,6 +58352,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{106B50CF-FD1D-4272-91A1-4C2C56B088EC}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A2:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -57283,8 +58493,725 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{250B58A3-FFB9-43FD-855D-5B3A680C69FD}">
+  <sheetPr codeName="Sheet6"/>
+  <dimension ref="A1:T43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="86" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="M1" s="86"/>
+      <c r="N1" s="86"/>
+      <c r="O1" s="86"/>
+      <c r="P1" s="86"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="58" t="s">
+        <v>486</v>
+      </c>
+      <c r="B3" s="58" t="s">
+        <v>492</v>
+      </c>
+      <c r="C3" t="s">
+        <v>452</v>
+      </c>
+      <c r="D3" t="s">
+        <v>514</v>
+      </c>
+      <c r="E3" t="s">
+        <v>515</v>
+      </c>
+      <c r="F3" t="s">
+        <v>490</v>
+      </c>
+      <c r="H3" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="82" t="s">
+        <v>491</v>
+      </c>
+      <c r="B4" s="87">
+        <v>0.30299999999999999</v>
+      </c>
+      <c r="C4" s="81">
+        <f>1/B4</f>
+        <v>3.3003300330033003</v>
+      </c>
+      <c r="D4">
+        <v>58.8</v>
+      </c>
+      <c r="E4">
+        <v>2500</v>
+      </c>
+      <c r="F4">
+        <v>19</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="58" t="s">
+        <v>517</v>
+      </c>
+      <c r="B5" s="87">
+        <f>AVERAGE(0.35,0.305,0.266)</f>
+        <v>0.307</v>
+      </c>
+      <c r="C5" s="81">
+        <f>1/B5</f>
+        <v>3.2573289902280131</v>
+      </c>
+      <c r="D5" s="79" t="s">
+        <v>516</v>
+      </c>
+      <c r="E5">
+        <v>2100</v>
+      </c>
+      <c r="F5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="58" t="s">
+        <v>486</v>
+      </c>
+      <c r="B8" s="58" t="s">
+        <v>492</v>
+      </c>
+      <c r="C8" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="58" t="s">
+        <v>535</v>
+      </c>
+      <c r="B9">
+        <f>AVERAGE(0.836,0.885,0.905)</f>
+        <v>0.87533333333333341</v>
+      </c>
+      <c r="C9">
+        <f>1/B9</f>
+        <v>1.1424219345011424</v>
+      </c>
+      <c r="D9" s="79" t="s">
+        <v>527</v>
+      </c>
+      <c r="E9">
+        <v>2600</v>
+      </c>
+      <c r="F9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="82" t="s">
+        <v>528</v>
+      </c>
+      <c r="B10">
+        <f>B9*(1-AVERAGE(0.1,0.15))</f>
+        <v>0.76591666666666669</v>
+      </c>
+      <c r="C10">
+        <f>1/B10</f>
+        <v>1.3056250680013055</v>
+      </c>
+      <c r="D10" s="79"/>
+      <c r="F10" s="79" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="58" t="s">
+        <v>536</v>
+      </c>
+      <c r="B11">
+        <f>1/C11</f>
+        <v>0.64890826648064182</v>
+      </c>
+      <c r="C11">
+        <f>AVERAGE(C4:C5)*(1-AVERAGE(0.52,0.54))</f>
+        <v>1.5410498704593585</v>
+      </c>
+      <c r="D11">
+        <v>50</v>
+      </c>
+      <c r="F11">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="58" t="s">
+        <v>543</v>
+      </c>
+      <c r="B12">
+        <f>1/C12</f>
+        <v>0.72615925058548003</v>
+      </c>
+      <c r="C12">
+        <f>AVERAGE(C4:C5)*(1-AVERAGE(0.58))</f>
+        <v>1.3771083948785758</v>
+      </c>
+      <c r="D12" s="79"/>
+      <c r="F12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="58" t="s">
+        <v>455</v>
+      </c>
+      <c r="B15" s="6">
+        <f>(AVERAGE(C4:C5)-AVERAGE(C10:C12))/AVERAGE(C4:C5)</f>
+        <v>0.57060049240377109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="58"/>
+      <c r="B16" s="6"/>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H17" s="16"/>
+    </row>
+    <row r="19" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H19" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="20" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H20" s="16" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>548</v>
+      </c>
+      <c r="D33" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>501</v>
+      </c>
+      <c r="B34" t="s">
+        <v>508</v>
+      </c>
+      <c r="D34" t="s">
+        <v>520</v>
+      </c>
+      <c r="E34" t="s">
+        <v>523</v>
+      </c>
+      <c r="F34" t="s">
+        <v>513</v>
+      </c>
+      <c r="G34" t="s">
+        <v>525</v>
+      </c>
+      <c r="H34" t="s">
+        <v>512</v>
+      </c>
+      <c r="I34" t="s">
+        <v>526</v>
+      </c>
+      <c r="J34" t="s">
+        <v>502</v>
+      </c>
+      <c r="M34" t="s">
+        <v>509</v>
+      </c>
+      <c r="P34" t="s">
+        <v>497</v>
+      </c>
+      <c r="S34" t="s">
+        <v>506</v>
+      </c>
+      <c r="T34" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>496</v>
+      </c>
+      <c r="B35" t="s">
+        <v>510</v>
+      </c>
+      <c r="C35" t="s">
+        <v>511</v>
+      </c>
+      <c r="J35" t="s">
+        <v>503</v>
+      </c>
+      <c r="K35" t="s">
+        <v>504</v>
+      </c>
+      <c r="L35" t="s">
+        <v>505</v>
+      </c>
+      <c r="M35" t="s">
+        <v>503</v>
+      </c>
+      <c r="N35" t="s">
+        <v>504</v>
+      </c>
+      <c r="O35" t="s">
+        <v>505</v>
+      </c>
+      <c r="P35" t="s">
+        <v>503</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>504</v>
+      </c>
+      <c r="R35" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>498</v>
+      </c>
+      <c r="B36" s="83">
+        <f>AVERAGE(S36:S37)</f>
+        <v>41.68</v>
+      </c>
+      <c r="C36" s="83">
+        <f>AVERAGE(T36:T37)</f>
+        <v>1840.7550000000001</v>
+      </c>
+      <c r="D36" s="83">
+        <v>213</v>
+      </c>
+      <c r="E36" s="84">
+        <v>0.38</v>
+      </c>
+      <c r="F36" s="83">
+        <f>C36*$E$4/$E$5*2*PI()/60</f>
+        <v>229.48025337534443</v>
+      </c>
+      <c r="G36" s="83">
+        <f>C36*$E$9/$E$5</f>
+        <v>2279.0300000000002</v>
+      </c>
+      <c r="H36" s="83">
+        <f>E36*D36</f>
+        <v>80.94</v>
+      </c>
+      <c r="I36" s="83">
+        <f>150*E36</f>
+        <v>57</v>
+      </c>
+      <c r="J36">
+        <v>8</v>
+      </c>
+      <c r="K36">
+        <v>22</v>
+      </c>
+      <c r="L36">
+        <v>70</v>
+      </c>
+      <c r="M36">
+        <v>8</v>
+      </c>
+      <c r="N36">
+        <v>23</v>
+      </c>
+      <c r="O36">
+        <v>52</v>
+      </c>
+      <c r="P36">
+        <v>884</v>
+      </c>
+      <c r="Q36">
+        <v>1711</v>
+      </c>
+      <c r="R36">
+        <v>2009</v>
+      </c>
+      <c r="S36">
+        <f>SUMPRODUCT(J36:L36,M36:O36)/SUM(J36:L36)</f>
+        <v>42.1</v>
+      </c>
+      <c r="T36">
+        <f>SUMPRODUCT(P36:R36,J36:L36)/SUM(J36:L36)</f>
+        <v>1853.44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B37" s="83"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="84"/>
+      <c r="J37">
+        <v>8</v>
+      </c>
+      <c r="K37">
+        <v>21</v>
+      </c>
+      <c r="L37">
+        <v>71</v>
+      </c>
+      <c r="M37">
+        <v>9</v>
+      </c>
+      <c r="N37">
+        <v>24</v>
+      </c>
+      <c r="O37">
+        <v>50</v>
+      </c>
+      <c r="P37">
+        <v>955</v>
+      </c>
+      <c r="Q37">
+        <v>1718</v>
+      </c>
+      <c r="R37">
+        <v>1959</v>
+      </c>
+      <c r="S37">
+        <f t="shared" ref="S37:S43" si="0">SUMPRODUCT(J37:L37,M37:O37)/SUM(J37:L37)</f>
+        <v>41.26</v>
+      </c>
+      <c r="T37">
+        <f t="shared" ref="T37:T43" si="1">SUMPRODUCT(P37:R37,J37:L37)/SUM(J37:L37)</f>
+        <v>1828.07</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>499</v>
+      </c>
+      <c r="B38" s="83">
+        <f>AVERAGE(S38:S40)</f>
+        <v>55.79</v>
+      </c>
+      <c r="C38" s="83">
+        <f>AVERAGE(T38:T39)</f>
+        <v>1791.8899999999999</v>
+      </c>
+      <c r="D38" s="83">
+        <v>215</v>
+      </c>
+      <c r="E38" s="84">
+        <v>0.48</v>
+      </c>
+      <c r="F38" s="83">
+        <f>C38*$E$4/$E$5*2*PI()/60</f>
+        <v>223.3884309540085</v>
+      </c>
+      <c r="G38" s="83">
+        <f>C38*$E$9/$E$5</f>
+        <v>2218.5304761904763</v>
+      </c>
+      <c r="H38" s="83">
+        <f>E38*D38</f>
+        <v>103.2</v>
+      </c>
+      <c r="I38" s="83">
+        <f>150*E38</f>
+        <v>72</v>
+      </c>
+      <c r="J38">
+        <v>4</v>
+      </c>
+      <c r="K38">
+        <v>25</v>
+      </c>
+      <c r="L38">
+        <v>71</v>
+      </c>
+      <c r="M38">
+        <v>13</v>
+      </c>
+      <c r="N38">
+        <v>33</v>
+      </c>
+      <c r="O38">
+        <v>66</v>
+      </c>
+      <c r="P38">
+        <v>1455</v>
+      </c>
+      <c r="Q38">
+        <v>1568</v>
+      </c>
+      <c r="R38">
+        <v>1767</v>
+      </c>
+      <c r="S38">
+        <f t="shared" si="0"/>
+        <v>55.63</v>
+      </c>
+      <c r="T38">
+        <f t="shared" si="1"/>
+        <v>1704.77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B39" s="83"/>
+      <c r="C39" s="83"/>
+      <c r="D39" s="83"/>
+      <c r="E39" s="84"/>
+      <c r="J39">
+        <v>3</v>
+      </c>
+      <c r="K39">
+        <v>27</v>
+      </c>
+      <c r="L39">
+        <v>70</v>
+      </c>
+      <c r="M39">
+        <v>13</v>
+      </c>
+      <c r="N39">
+        <v>35</v>
+      </c>
+      <c r="O39">
+        <v>68</v>
+      </c>
+      <c r="P39">
+        <v>1543</v>
+      </c>
+      <c r="Q39">
+        <v>1696</v>
+      </c>
+      <c r="R39">
+        <v>1964</v>
+      </c>
+      <c r="S39">
+        <f t="shared" si="0"/>
+        <v>57.44</v>
+      </c>
+      <c r="T39">
+        <f t="shared" si="1"/>
+        <v>1879.01</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B40" s="83"/>
+      <c r="C40" s="83"/>
+      <c r="D40" s="83"/>
+      <c r="E40" s="84"/>
+      <c r="J40">
+        <v>3</v>
+      </c>
+      <c r="K40">
+        <v>24</v>
+      </c>
+      <c r="L40">
+        <v>73</v>
+      </c>
+      <c r="M40">
+        <v>13</v>
+      </c>
+      <c r="N40">
+        <v>33</v>
+      </c>
+      <c r="O40">
+        <v>63</v>
+      </c>
+      <c r="P40">
+        <v>905</v>
+      </c>
+      <c r="Q40">
+        <v>1541</v>
+      </c>
+      <c r="R40">
+        <v>1827</v>
+      </c>
+      <c r="S40">
+        <f t="shared" si="0"/>
+        <v>54.3</v>
+      </c>
+      <c r="T40">
+        <f t="shared" si="1"/>
+        <v>1730.7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>500</v>
+      </c>
+      <c r="B41" s="83">
+        <f>AVERAGE(S41:S43)</f>
+        <v>73.423333333333332</v>
+      </c>
+      <c r="C41" s="83">
+        <f>AVERAGE(T41:T42)</f>
+        <v>1395.97</v>
+      </c>
+      <c r="D41" s="83">
+        <v>220</v>
+      </c>
+      <c r="E41" s="84">
+        <v>0.59</v>
+      </c>
+      <c r="F41" s="83">
+        <f>C41*$E$4/$E$5*2*PI()/60</f>
+        <v>174.0305197076089</v>
+      </c>
+      <c r="G41" s="83">
+        <f>C41*$E$9/$E$5</f>
+        <v>1728.3438095238096</v>
+      </c>
+      <c r="H41" s="83">
+        <f>E41*D41</f>
+        <v>129.79999999999998</v>
+      </c>
+      <c r="I41" s="83">
+        <f>150*E41</f>
+        <v>88.5</v>
+      </c>
+      <c r="J41">
+        <v>41</v>
+      </c>
+      <c r="K41">
+        <v>59</v>
+      </c>
+      <c r="M41">
+        <v>37</v>
+      </c>
+      <c r="N41">
+        <v>76</v>
+      </c>
+      <c r="P41">
+        <v>904</v>
+      </c>
+      <c r="Q41">
+        <v>1514</v>
+      </c>
+      <c r="S41">
+        <f t="shared" si="0"/>
+        <v>60.01</v>
+      </c>
+      <c r="T41">
+        <f t="shared" si="1"/>
+        <v>1263.9000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J42">
+        <v>4</v>
+      </c>
+      <c r="K42">
+        <v>96</v>
+      </c>
+      <c r="M42">
+        <v>36</v>
+      </c>
+      <c r="N42">
+        <v>81</v>
+      </c>
+      <c r="P42">
+        <v>1433</v>
+      </c>
+      <c r="Q42">
+        <v>1532</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="0"/>
+        <v>79.2</v>
+      </c>
+      <c r="T42">
+        <f t="shared" si="1"/>
+        <v>1528.04</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J43">
+        <v>2</v>
+      </c>
+      <c r="K43">
+        <v>98</v>
+      </c>
+      <c r="M43">
+        <v>35</v>
+      </c>
+      <c r="N43">
+        <v>82</v>
+      </c>
+      <c r="P43">
+        <v>1492</v>
+      </c>
+      <c r="Q43">
+        <v>1545</v>
+      </c>
+      <c r="S43">
+        <f t="shared" si="0"/>
+        <v>81.06</v>
+      </c>
+      <c r="T43">
+        <f t="shared" si="1"/>
+        <v>1543.94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{618CB0D2-6B6A-46CD-AA73-BC2E859F7E4A}">
-  <sheetPr>
+  <sheetPr codeName="Sheet7">
     <tabColor theme="1" tint="0.34998626667073579"/>
   </sheetPr>
   <dimension ref="A1:K38"/>
@@ -57921,9 +59848,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2F2E001-C6A6-4410-8BDA-651DE4E25875}">
-  <sheetPr>
+  <sheetPr codeName="Sheet8">
     <tabColor theme="1" tint="0.34998626667073579"/>
   </sheetPr>
   <dimension ref="A1:U40"/>
@@ -57956,12 +59883,12 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="D3" s="84" t="s">
+      <c r="D3" s="92" t="s">
         <v>333</v>
       </c>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
       <c r="I3" s="2" t="s">
         <v>334</v>
       </c>
@@ -59685,12 +61612,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0CAEE4D-8CD0-45E7-B56A-DDFD62CED9DB}">
-  <sheetPr>
+  <sheetPr codeName="Sheet9">
     <tabColor theme="1" tint="0.34998626667073579"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.28515625" style="58" customWidth="1"/>
@@ -59921,6 +61848,125 @@
         <v>418</v>
       </c>
     </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="58">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>489</v>
+      </c>
+      <c r="C12" s="58">
+        <v>2014</v>
+      </c>
+      <c r="D12" t="s">
+        <v>488</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="58">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>495</v>
+      </c>
+      <c r="C13" s="58">
+        <v>2016</v>
+      </c>
+      <c r="D13" t="s">
+        <v>494</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="58">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>531</v>
+      </c>
+      <c r="C14" s="58">
+        <v>2020</v>
+      </c>
+      <c r="D14" t="s">
+        <v>529</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="58">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>534</v>
+      </c>
+      <c r="C15" s="58">
+        <v>2022</v>
+      </c>
+      <c r="D15" t="s">
+        <v>532</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="58">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>539</v>
+      </c>
+      <c r="C16" s="58">
+        <v>2021</v>
+      </c>
+      <c r="D16" t="s">
+        <v>538</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="58">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>542</v>
+      </c>
+      <c r="C17" s="58">
+        <v>2018</v>
+      </c>
+      <c r="D17" t="s">
+        <v>541</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="58">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="58">
+        <v>2015</v>
+      </c>
+      <c r="D18" t="s">
+        <v>546</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>545</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{DE7379BF-EEAF-41D0-8544-8C59522809F9}"/>
@@ -59933,879 +61979,14 @@
     <hyperlink ref="E9" r:id="rId8" xr:uid="{761034BB-8A27-4001-900F-3C41BCC642F6}"/>
     <hyperlink ref="E10" r:id="rId9" xr:uid="{8536D162-00D0-4BEC-8CC0-660CD1803D1F}"/>
     <hyperlink ref="E11" r:id="rId10" xr:uid="{EE7664BF-45CA-4A06-A914-5F66C8749376}"/>
+    <hyperlink ref="E12" r:id="rId11" xr:uid="{54624FBF-D8CC-46F2-9730-903E0115D238}"/>
+    <hyperlink ref="E13" r:id="rId12" xr:uid="{C24D70DB-8D05-43D1-97EB-D42B8AED8951}"/>
+    <hyperlink ref="E14" r:id="rId13" xr:uid="{C500BA1B-03A0-4BBE-B949-31FED03077C8}"/>
+    <hyperlink ref="E15" r:id="rId14" xr:uid="{5E5B5C69-2A61-4A89-AAC9-5E7540C84A78}"/>
+    <hyperlink ref="E16" r:id="rId15" xr:uid="{401984CD-5D55-4E3F-9838-DEB96C5FA2B6}"/>
+    <hyperlink ref="E17" r:id="rId16" xr:uid="{F00C44D4-0A9F-457C-B6BE-274854BBE155}"/>
+    <hyperlink ref="E18" r:id="rId17" xr:uid="{1746CAFD-047E-4713-8136-AAE6F8474EA4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA4BAC4-DAD5-4B3C-8999-FA6866E1C28D}">
-  <dimension ref="B1:J26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="45.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="11.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D1" s="66" t="s">
-        <v>314</v>
-      </c>
-      <c r="E1" s="66" t="s">
-        <v>316</v>
-      </c>
-      <c r="F1" s="66" t="s">
-        <v>317</v>
-      </c>
-      <c r="G1" s="66" t="s">
-        <v>318</v>
-      </c>
-      <c r="H1" s="66" t="s">
-        <v>320</v>
-      </c>
-      <c r="I1" s="66" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>456</v>
-      </c>
-      <c r="C2" t="s">
-        <v>484</v>
-      </c>
-      <c r="D2" s="6">
-        <f>IF($C2="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C2,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.22712128261679607</v>
-      </c>
-      <c r="E2" s="6">
-        <f>IF($C2="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C2,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.18096501818637736</v>
-      </c>
-      <c r="F2" s="6">
-        <f>IF($C2="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C2,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.20705409259653504</v>
-      </c>
-      <c r="G2" s="6">
-        <f>IF($C2="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C2,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>9.990108165832158E-2</v>
-      </c>
-      <c r="H2" s="6">
-        <f>IF($C2="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C2,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>6.4928393115227967E-2</v>
-      </c>
-      <c r="I2" s="6">
-        <f>IF($C2="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C2,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.22003013182674194</v>
-      </c>
-      <c r="J2" s="4"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>457</v>
-      </c>
-      <c r="C3" t="s">
-        <v>484</v>
-      </c>
-      <c r="D3" s="6">
-        <f>IF($C3="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C3,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.22712128261679607</v>
-      </c>
-      <c r="E3" s="6">
-        <f>IF($C3="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C3,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.18096501818637736</v>
-      </c>
-      <c r="F3" s="6">
-        <f>IF($C3="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C3,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.20705409259653504</v>
-      </c>
-      <c r="G3" s="6">
-        <f>IF($C3="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C3,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>9.990108165832158E-2</v>
-      </c>
-      <c r="H3" s="6">
-        <f>IF($C3="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C3,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>6.4928393115227967E-2</v>
-      </c>
-      <c r="I3" s="6">
-        <f>IF($C3="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C3,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.22003013182674194</v>
-      </c>
-      <c r="J3" s="4"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>458</v>
-      </c>
-      <c r="C4" t="s">
-        <v>356</v>
-      </c>
-      <c r="D4" s="6">
-        <f>IF($C4="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C4,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.03</v>
-      </c>
-      <c r="E4" s="6">
-        <f>IF($C4="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C4,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="F4" s="6">
-        <f>IF($C4="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C4,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.15</v>
-      </c>
-      <c r="G4" s="6">
-        <f>IF($C4="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C4,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.02</v>
-      </c>
-      <c r="H4" s="6">
-        <f>IF($C4="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C4,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.23</v>
-      </c>
-      <c r="I4" s="6">
-        <f>IF($C4="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C4,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="4"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>459</v>
-      </c>
-      <c r="C5" t="s">
-        <v>484</v>
-      </c>
-      <c r="D5" s="6">
-        <f>IF($C5="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C5,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.22712128261679607</v>
-      </c>
-      <c r="E5" s="6">
-        <f>IF($C5="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C5,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.18096501818637736</v>
-      </c>
-      <c r="F5" s="6">
-        <f>IF($C5="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C5,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.20705409259653504</v>
-      </c>
-      <c r="G5" s="6">
-        <f>IF($C5="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C5,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>9.990108165832158E-2</v>
-      </c>
-      <c r="H5" s="6">
-        <f>IF($C5="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C5,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>6.4928393115227967E-2</v>
-      </c>
-      <c r="I5" s="6">
-        <f>IF($C5="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C5,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.22003013182674194</v>
-      </c>
-      <c r="J5" s="4"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>460</v>
-      </c>
-      <c r="C6" t="s">
-        <v>361</v>
-      </c>
-      <c r="D6" s="6">
-        <f>IF($C6="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C6,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="E6" s="6">
-        <f>IF($C6="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C6,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.43</v>
-      </c>
-      <c r="F6" s="6">
-        <f>IF($C6="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C6,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
-        <f>IF($C6="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C6,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.02</v>
-      </c>
-      <c r="H6" s="6">
-        <f>IF($C6="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C6,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="6">
-        <f>IF($C6="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C6,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="4"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>461</v>
-      </c>
-      <c r="C7" t="s">
-        <v>362</v>
-      </c>
-      <c r="D7" s="6">
-        <f>IF($C7="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C7,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.37818181818181817</v>
-      </c>
-      <c r="E7" s="6">
-        <f>IF($C7="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C7,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.18242424242424241</v>
-      </c>
-      <c r="F7" s="6">
-        <f>IF($C7="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C7,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.26363636363636361</v>
-      </c>
-      <c r="G7" s="6">
-        <f>IF($C7="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C7,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.17575757575757572</v>
-      </c>
-      <c r="H7" s="6">
-        <f>IF($C7="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C7,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="6">
-        <f>IF($C7="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C7,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="4"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>462</v>
-      </c>
-      <c r="C8" t="s">
-        <v>363</v>
-      </c>
-      <c r="D8" s="6">
-        <f>IF($C8="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C8,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>9.4117647058823542E-2</v>
-      </c>
-      <c r="E8" s="6">
-        <f>IF($C8="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C8,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.17058823529411765</v>
-      </c>
-      <c r="F8" s="6">
-        <f>IF($C8="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C8,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.44117647058823534</v>
-      </c>
-      <c r="G8" s="6">
-        <f>IF($C8="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C8,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.29411764705882354</v>
-      </c>
-      <c r="H8" s="6">
-        <f>IF($C8="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C8,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="6">
-        <f>IF($C8="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C8,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="4"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>463</v>
-      </c>
-      <c r="C9" t="s">
-        <v>364</v>
-      </c>
-      <c r="D9" s="6">
-        <f>IF($C9="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C9,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.33</v>
-      </c>
-      <c r="E9" s="6">
-        <f>IF($C9="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C9,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.1</v>
-      </c>
-      <c r="F9" s="6">
-        <f>IF($C9="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C9,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.15</v>
-      </c>
-      <c r="G9" s="6">
-        <f>IF($C9="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C9,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="6">
-        <f>IF($C9="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C9,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.42</v>
-      </c>
-      <c r="I9" s="6">
-        <f>IF($C9="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C9,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>464</v>
-      </c>
-      <c r="C10" t="s">
-        <v>365</v>
-      </c>
-      <c r="D10" s="6">
-        <f>IF($C10="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C10,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.08</v>
-      </c>
-      <c r="E10" s="6">
-        <f>IF($C10="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C10,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.18</v>
-      </c>
-      <c r="F10" s="6">
-        <f>IF($C10="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C10,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.46</v>
-      </c>
-      <c r="G10" s="6">
-        <f>IF($C10="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C10,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.27</v>
-      </c>
-      <c r="H10" s="6">
-        <f>IF($C10="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C10,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="6">
-        <f>IF($C10="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C10,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.01</v>
-      </c>
-      <c r="J10" s="4"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>465</v>
-      </c>
-      <c r="C11" t="s">
-        <v>356</v>
-      </c>
-      <c r="D11" s="6">
-        <f>IF($C11="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C11,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.03</v>
-      </c>
-      <c r="E11" s="6">
-        <f>IF($C11="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C11,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="F11" s="6">
-        <f>IF($C11="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C11,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.15</v>
-      </c>
-      <c r="G11" s="6">
-        <f>IF($C11="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C11,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.02</v>
-      </c>
-      <c r="H11" s="6">
-        <f>IF($C11="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C11,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.23</v>
-      </c>
-      <c r="I11" s="6">
-        <f>IF($C11="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C11,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="4"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>466</v>
-      </c>
-      <c r="C12" t="s">
-        <v>366</v>
-      </c>
-      <c r="D12" s="6">
-        <f>IF($C12="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C12,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.04</v>
-      </c>
-      <c r="E12" s="6">
-        <f>IF($C12="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C12,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.38</v>
-      </c>
-      <c r="F12" s="6">
-        <f>IF($C12="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C12,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="G12" s="6">
-        <f>IF($C12="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C12,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="6">
-        <f>IF($C12="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C12,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="6">
-        <f>IF($C12="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C12,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>467</v>
-      </c>
-      <c r="C13" t="s">
-        <v>347</v>
-      </c>
-      <c r="D13" s="6">
-        <f>IF($C13="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C13,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="6">
-        <f>IF($C13="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C13,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="6">
-        <f>IF($C13="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C13,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="6">
-        <f>IF($C13="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C13,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>1.9230769230769232E-2</v>
-      </c>
-      <c r="H13" s="6">
-        <f>IF($C13="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C13,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>5.7692307692307696E-2</v>
-      </c>
-      <c r="I13" s="6">
-        <f>IF($C13="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C13,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.92307692307692302</v>
-      </c>
-      <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>468</v>
-      </c>
-      <c r="C14" t="s">
-        <v>367</v>
-      </c>
-      <c r="D14" s="6">
-        <f>IF($C14="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C14,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="6">
-        <f>IF($C14="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C14,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="6">
-        <f>IF($C14="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C14,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.16</v>
-      </c>
-      <c r="G14" s="6">
-        <f>IF($C14="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C14,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="6">
-        <f>IF($C14="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C14,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="6">
-        <f>IF($C14="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C14,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.84</v>
-      </c>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>469</v>
-      </c>
-      <c r="C15" t="s">
-        <v>368</v>
-      </c>
-      <c r="D15" s="6">
-        <f>IF($C15="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C15,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>4.5197740112994352E-3</v>
-      </c>
-      <c r="E15" s="6">
-        <f>IF($C15="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C15,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>3.0131826741996233E-3</v>
-      </c>
-      <c r="F15" s="6">
-        <f>IF($C15="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C15,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>5.6497175141242938E-3</v>
-      </c>
-      <c r="G15" s="6">
-        <f>IF($C15="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C15,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>9.4161958568738224E-3</v>
-      </c>
-      <c r="H15" s="6">
-        <f>IF($C15="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C15,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>1.6949152542372881E-2</v>
-      </c>
-      <c r="I15" s="6">
-        <f>IF($C15="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C15,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.96045197740112986</v>
-      </c>
-      <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>470</v>
-      </c>
-      <c r="C16" t="s">
-        <v>369</v>
-      </c>
-      <c r="D16" s="6">
-        <f>IF($C16="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C16,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.3</v>
-      </c>
-      <c r="E16" s="6">
-        <f>IF($C16="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C16,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="6">
-        <f>IF($C16="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C16,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="6">
-        <f>IF($C16="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C16,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.06</v>
-      </c>
-      <c r="H16" s="6">
-        <f>IF($C16="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C16,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.15</v>
-      </c>
-      <c r="I16" s="6">
-        <f>IF($C16="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C16,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.49</v>
-      </c>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>471</v>
-      </c>
-      <c r="C17" t="s">
-        <v>374</v>
-      </c>
-      <c r="D17" s="6">
-        <f>IF($C17="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C17,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.33488372093023255</v>
-      </c>
-      <c r="E17" s="6">
-        <f>IF($C17="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C17,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.14961240310077517</v>
-      </c>
-      <c r="F17" s="6">
-        <f>IF($C17="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C17,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.19767441860465118</v>
-      </c>
-      <c r="G17" s="6">
-        <f>IF($C17="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C17,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.13178294573643412</v>
-      </c>
-      <c r="H17" s="6">
-        <f>IF($C17="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C17,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="6">
-        <f>IF($C17="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C17,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.18604651162790697</v>
-      </c>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>472</v>
-      </c>
-      <c r="C18" t="s">
-        <v>372</v>
-      </c>
-      <c r="D18" s="6">
-        <f>IF($C18="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C18,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.33488372093023255</v>
-      </c>
-      <c r="E18" s="6">
-        <f>IF($C18="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C18,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.14961240310077517</v>
-      </c>
-      <c r="F18" s="6">
-        <f>IF($C18="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C18,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.19767441860465118</v>
-      </c>
-      <c r="G18" s="6">
-        <f>IF($C18="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C18,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.13178294573643412</v>
-      </c>
-      <c r="H18" s="6">
-        <f>IF($C18="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C18,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="6">
-        <f>IF($C18="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C18,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.18604651162790697</v>
-      </c>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>473</v>
-      </c>
-      <c r="C19" t="s">
-        <v>370</v>
-      </c>
-      <c r="D19" s="6">
-        <f>IF($C19="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C19,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.26046511627906982</v>
-      </c>
-      <c r="E19" s="6">
-        <f>IF($C19="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C19,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.1</v>
-      </c>
-      <c r="F19" s="6">
-        <f>IF($C19="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C19,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.10465116279069767</v>
-      </c>
-      <c r="G19" s="6">
-        <f>IF($C19="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C19,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.12209302325581395</v>
-      </c>
-      <c r="H19" s="6">
-        <f>IF($C19="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C19,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.15697674418604651</v>
-      </c>
-      <c r="I19" s="6">
-        <f>IF($C19="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C19,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.2558139534883721</v>
-      </c>
-      <c r="J19" s="4"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>474</v>
-      </c>
-      <c r="C20" t="s">
-        <v>370</v>
-      </c>
-      <c r="D20" s="6">
-        <f>IF($C20="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C20,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.26046511627906982</v>
-      </c>
-      <c r="E20" s="6">
-        <f>IF($C20="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C20,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.1</v>
-      </c>
-      <c r="F20" s="6">
-        <f>IF($C20="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C20,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.10465116279069767</v>
-      </c>
-      <c r="G20" s="6">
-        <f>IF($C20="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C20,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.12209302325581395</v>
-      </c>
-      <c r="H20" s="6">
-        <f>IF($C20="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C20,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.15697674418604651</v>
-      </c>
-      <c r="I20" s="6">
-        <f>IF($C20="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C20,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.2558139534883721</v>
-      </c>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>475</v>
-      </c>
-      <c r="C21" t="s">
-        <v>371</v>
-      </c>
-      <c r="D21" s="6">
-        <f>IF($C21="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C21,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.33488372093023255</v>
-      </c>
-      <c r="E21" s="6">
-        <f>IF($C21="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C21,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.14961240310077517</v>
-      </c>
-      <c r="F21" s="6">
-        <f>IF($C21="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C21,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.19767441860465118</v>
-      </c>
-      <c r="G21" s="6">
-        <f>IF($C21="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C21,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.13178294573643412</v>
-      </c>
-      <c r="H21" s="6">
-        <f>IF($C21="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C21,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="6">
-        <f>IF($C21="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C21,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.18604651162790697</v>
-      </c>
-      <c r="J21" s="4"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>476</v>
-      </c>
-      <c r="C22" t="s">
-        <v>371</v>
-      </c>
-      <c r="D22" s="6">
-        <f>IF($C22="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C22,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.33488372093023255</v>
-      </c>
-      <c r="E22" s="6">
-        <f>IF($C22="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C22,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.14961240310077517</v>
-      </c>
-      <c r="F22" s="6">
-        <f>IF($C22="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C22,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.19767441860465118</v>
-      </c>
-      <c r="G22" s="6">
-        <f>IF($C22="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C22,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.13178294573643412</v>
-      </c>
-      <c r="H22" s="6">
-        <f>IF($C22="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C22,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="I22" s="6">
-        <f>IF($C22="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C22,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.18604651162790697</v>
-      </c>
-      <c r="J22" s="4"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>477</v>
-      </c>
-      <c r="C23" t="s">
-        <v>375</v>
-      </c>
-      <c r="D23" s="6">
-        <f>IF($C23="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C23,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.33488372093023255</v>
-      </c>
-      <c r="E23" s="6">
-        <f>IF($C23="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C23,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.14961240310077517</v>
-      </c>
-      <c r="F23" s="6">
-        <f>IF($C23="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C23,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.19767441860465118</v>
-      </c>
-      <c r="G23" s="6">
-        <f>IF($C23="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C23,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.13178294573643412</v>
-      </c>
-      <c r="H23" s="6">
-        <f>IF($C23="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C23,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="6">
-        <f>IF($C23="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C23,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.18604651162790697</v>
-      </c>
-      <c r="J23" s="4"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>478</v>
-      </c>
-      <c r="C24" t="s">
-        <v>484</v>
-      </c>
-      <c r="D24" s="6">
-        <f>IF($C24="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C24,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.22712128261679607</v>
-      </c>
-      <c r="E24" s="6">
-        <f>IF($C24="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C24,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.18096501818637736</v>
-      </c>
-      <c r="F24" s="6">
-        <f>IF($C24="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C24,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.20705409259653504</v>
-      </c>
-      <c r="G24" s="6">
-        <f>IF($C24="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C24,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>9.990108165832158E-2</v>
-      </c>
-      <c r="H24" s="6">
-        <f>IF($C24="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C24,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>6.4928393115227967E-2</v>
-      </c>
-      <c r="I24" s="6">
-        <f>IF($C24="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C24,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.22003013182674194</v>
-      </c>
-      <c r="J24" s="4"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>479</v>
-      </c>
-      <c r="C25" t="s">
-        <v>484</v>
-      </c>
-      <c r="D25" s="6">
-        <f>IF($C25="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C25,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.22712128261679607</v>
-      </c>
-      <c r="E25" s="6">
-        <f>IF($C25="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C25,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.18096501818637736</v>
-      </c>
-      <c r="F25" s="6">
-        <f>IF($C25="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C25,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.20705409259653504</v>
-      </c>
-      <c r="G25" s="6">
-        <f>IF($C25="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C25,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>9.990108165832158E-2</v>
-      </c>
-      <c r="H25" s="6">
-        <f>IF($C25="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C25,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>6.4928393115227967E-2</v>
-      </c>
-      <c r="I25" s="6">
-        <f>IF($C25="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C25,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.22003013182674194</v>
-      </c>
-      <c r="J25" s="4"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>480</v>
-      </c>
-      <c r="C26" t="s">
-        <v>484</v>
-      </c>
-      <c r="D26" s="6">
-        <f>IF($C26="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C26,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.22712128261679607</v>
-      </c>
-      <c r="E26" s="6">
-        <f>IF($C26="average",Efficiencies!D$27,INDEX('Temperature Breakdown'!E$25:E$40,MATCH(Mapping!$C26,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.18096501818637736</v>
-      </c>
-      <c r="F26" s="6">
-        <f>IF($C26="average",Efficiencies!E$27,INDEX('Temperature Breakdown'!F$25:F$40,MATCH(Mapping!$C26,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.20705409259653504</v>
-      </c>
-      <c r="G26" s="6">
-        <f>IF($C26="average",Efficiencies!F$27,INDEX('Temperature Breakdown'!G$25:G$40,MATCH(Mapping!$C26,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>9.990108165832158E-2</v>
-      </c>
-      <c r="H26" s="6">
-        <f>IF($C26="average",Efficiencies!G$27,INDEX('Temperature Breakdown'!H$25:H$40,MATCH(Mapping!$C26,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>6.4928393115227967E-2</v>
-      </c>
-      <c r="I26" s="6">
-        <f>IF($C26="average",Efficiencies!H$27,INDEX('Temperature Breakdown'!I$25:I$40,MATCH(Mapping!$C26,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
-        <v>0.22003013182674194</v>
-      </c>
-      <c r="J26" s="4"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="D2:I26">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/InputData/indst/PIFURfE/Perc Indst Fuel Use Reduction for Elec.xlsx
+++ b/InputData/indst/PIFURfE/Perc Indst Fuel Use Reduction for Elec.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\indst\PIFURfE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A914897-6198-4BC4-8C8A-3ACA6E0D593F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C56811-62A1-4707-B244-DCD9C31410F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26790" yWindow="435" windowWidth="24225" windowHeight="16620" tabRatio="756" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -322,7 +322,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9083" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9090" uniqueCount="555">
   <si>
     <t>Percentage Industry Fuel Use Reduction for Electricity</t>
   </si>
@@ -1114,30 +1114,6 @@
   </si>
   <si>
     <t>We will use some representative technologies below to form our estimate.</t>
-  </si>
-  <si>
-    <t>boilers</t>
-  </si>
-  <si>
-    <t>electrochemical</t>
-  </si>
-  <si>
-    <t>machine drive</t>
-  </si>
-  <si>
-    <t>other process</t>
-  </si>
-  <si>
-    <t>nonboiler high temp</t>
-  </si>
-  <si>
-    <t>nonboiler low temp</t>
-  </si>
-  <si>
-    <t>nonboiler med temp</t>
-  </si>
-  <si>
-    <t>cooling</t>
   </si>
   <si>
     <t xml:space="preserve">Released: February 2021 </t>
@@ -1996,6 +1972,48 @@
   <si>
     <t>Ref 20</t>
   </si>
+  <si>
+    <t>Nonboiler low temp</t>
+  </si>
+  <si>
+    <t>Nonboiler med temp</t>
+  </si>
+  <si>
+    <t>Nonboiler high temp</t>
+  </si>
+  <si>
+    <t>Cooling</t>
+  </si>
+  <si>
+    <t>Machine Drive</t>
+  </si>
+  <si>
+    <t>Other process</t>
+  </si>
+  <si>
+    <t>Facility HVAC</t>
+  </si>
+  <si>
+    <t>Facility Lighting</t>
+  </si>
+  <si>
+    <t>Other Nonprocess</t>
+  </si>
+  <si>
+    <t>efficiency of heat pump for HVAC</t>
+  </si>
+  <si>
+    <t>average HVAC boiler efficiency</t>
+  </si>
+  <si>
+    <t>and for HVAC applications:</t>
+  </si>
+  <si>
+    <t>For lighting, we assume fuel combustion for lighting must be running generators to power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lighting units. The efficiency of a diesel generator is around 35%. </t>
+  </si>
 </sst>
 </file>
 
@@ -2376,9 +2394,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="5" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2386,6 +2401,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="5" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5572,7 +5590,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="59.28515625" customWidth="1"/>
@@ -5608,7 +5626,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -5693,12 +5711,12 @@
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
@@ -5708,22 +5726,22 @@
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" s="14" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -5733,22 +5751,22 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B38" s="14" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -5782,6 +5800,21 @@
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>210</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="4">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -5807,30 +5840,30 @@
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D1" s="66" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="E1" s="66" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="F1" s="66" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G1" s="66" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="H1" s="66" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="I1" s="66" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="C2" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="D2" s="6">
         <f>IF($C2="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C2,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -5860,10 +5893,10 @@
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="C3" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="D3" s="6">
         <f>IF($C3="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C3,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -5893,10 +5926,10 @@
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="C4" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="D4" s="6">
         <f>IF($C4="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C4,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -5926,10 +5959,10 @@
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C5" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="D5" s="6">
         <f>IF($C5="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C5,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -5959,10 +5992,10 @@
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="C6" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="D6" s="6">
         <f>IF($C6="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C6,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -5992,10 +6025,10 @@
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C7" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="D7" s="6">
         <f>IF($C7="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C7,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6025,10 +6058,10 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="C8" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="D8" s="6">
         <f>IF($C8="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C8,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6058,10 +6091,10 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C9" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="D9" s="6">
         <f>IF($C9="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C9,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6091,10 +6124,10 @@
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C10" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="D10" s="6">
         <f>IF($C10="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C10,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6124,10 +6157,10 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C11" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="D11" s="6">
         <f>IF($C11="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C11,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6157,10 +6190,10 @@
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C12" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D12" s="6">
         <f>IF($C12="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C12,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6190,10 +6223,10 @@
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="C13" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="D13" s="6">
         <f>IF($C13="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C13,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6223,10 +6256,10 @@
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="C14" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="D14" s="6">
         <f>IF($C14="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C14,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6256,10 +6289,10 @@
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C15" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="D15" s="6">
         <f>IF($C15="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C15,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6289,10 +6322,10 @@
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="C16" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="D16" s="6">
         <f>IF($C16="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C16,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6322,10 +6355,10 @@
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C17" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="D17" s="6">
         <f>IF($C17="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C17,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6355,10 +6388,10 @@
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="C18" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="D18" s="6">
         <f>IF($C18="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C18,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6388,10 +6421,10 @@
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="C19" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="D19" s="6">
         <f>IF($C19="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C19,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6421,10 +6454,10 @@
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="C20" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="D20" s="6">
         <f>IF($C20="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C20,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6454,10 +6487,10 @@
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="C21" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="D21" s="6">
         <f>IF($C21="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C21,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6487,10 +6520,10 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="C22" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="D22" s="6">
         <f>IF($C22="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C22,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6520,10 +6553,10 @@
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C23" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="D23" s="6">
         <f>IF($C23="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C23,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6553,10 +6586,10 @@
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="C24" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="D24" s="6">
         <f>IF($C24="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C24,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6586,10 +6619,10 @@
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="C25" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="D25" s="6">
         <f>IF($C25="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C25,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6619,10 +6652,10 @@
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="C26" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="D26" s="6">
         <f>IF($C26="average",Efficiencies!C$27,INDEX('Temperature Breakdown'!D$25:D$40,MATCH(Mapping!$C26,'Temperature Breakdown'!$A$25:$A$40,0)))</f>
@@ -6672,45 +6705,52 @@
   <sheetPr codeName="Sheet11">
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="9" width="17.42578125" customWidth="1"/>
+    <col min="2" max="7" width="17.42578125" customWidth="1"/>
+    <col min="8" max="11" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>264</v>
+        <v>473</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>269</v>
+        <v>541</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>270</v>
+        <v>542</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>268</v>
+        <v>543</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>271</v>
+        <v>544</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>266</v>
+        <v>545</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>265</v>
-      </c>
-      <c r="I1" s="18" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>546</v>
+      </c>
+      <c r="I1" t="s">
+        <v>547</v>
+      </c>
+      <c r="J1" t="s">
+        <v>548</v>
+      </c>
+      <c r="K1" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="B2" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D2:I2)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D2:I2),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -6737,17 +6777,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H2" s="81">
-        <f>AVERAGE(C2:G2)</f>
-        <v>0.5732623635641757</v>
-      </c>
-      <c r="I2" s="85">
+        <f t="shared" ref="H2:H3" si="0">AVERAGE(B2:G2)</f>
+        <v>0.57509219870122874</v>
+      </c>
+      <c r="I2" s="81">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J2" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K2" s="85">
         <f>Other!B15</f>
         <v>0.57060049240377109</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="B3" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D3:I3)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D3:I3),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -6774,17 +6822,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H3" s="81">
-        <f t="shared" ref="H3:H26" si="0">AVERAGE(C3:G3)</f>
-        <v>0.5732623635641757</v>
-      </c>
-      <c r="I3" s="85">
-        <f>I2</f>
+        <f t="shared" si="0"/>
+        <v>0.57509219870122874</v>
+      </c>
+      <c r="I3" s="81">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J3" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K3" s="85">
+        <f>K2</f>
         <v>0.57060049240377109</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="B4" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D4:I4)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D4:I4),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -6811,17 +6867,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H4" s="81">
-        <f t="shared" si="0"/>
-        <v>0.55643026112613903</v>
+        <f>AVERAGE(B4:G4)</f>
+        <v>0.56227504925494742</v>
       </c>
       <c r="I4" s="81">
-        <f t="shared" ref="I4:I25" si="3">H4</f>
-        <v>0.55643026112613903</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J4" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K4" s="81">
+        <f>AVERAGE(B4:J4)</f>
+        <v>0.59478535576972102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="B5" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D5:I5)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D5:I5),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -6848,17 +6912,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H5" s="81">
-        <f t="shared" si="0"/>
-        <v>0.5732623635641757</v>
-      </c>
-      <c r="I5" s="85">
-        <f>I2</f>
+        <f t="shared" ref="H5:H26" si="3">AVERAGE(B5:G5)</f>
+        <v>0.57509219870122874</v>
+      </c>
+      <c r="I5" s="81">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J5" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K5" s="85">
+        <f>K2</f>
         <v>0.57060049240377109</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="B6" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D6:I6)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D6:I6),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -6885,17 +6957,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H6" s="81">
-        <f t="shared" si="0"/>
-        <v>0.54967748294789121</v>
+        <f t="shared" si="3"/>
+        <v>0.58103185127419832</v>
       </c>
       <c r="I6" s="81">
-        <f t="shared" si="3"/>
-        <v>0.54967748294789121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J6" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K6" s="81">
+        <f t="shared" ref="K6:K25" si="4">AVERAGE(B6:J6)</f>
+        <v>0.60937397956247175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="B7" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D7:I7)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D7:I7),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -6922,17 +7002,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H7" s="81">
-        <f t="shared" si="0"/>
-        <v>0.54177106856603507</v>
+        <f t="shared" si="3"/>
+        <v>0.55192696635659533</v>
       </c>
       <c r="I7" s="81">
-        <f t="shared" si="3"/>
-        <v>0.54177106856603507</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J7" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K7" s="81">
+        <f t="shared" si="4"/>
+        <v>0.58673684684878047</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="B8" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D8:I8)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D8:I8),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -6959,17 +7047,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H8" s="81">
-        <f t="shared" si="0"/>
-        <v>0.5251619721548294</v>
+        <f t="shared" si="3"/>
+        <v>0.51147059488130908</v>
       </c>
       <c r="I8" s="81">
-        <f t="shared" si="3"/>
-        <v>0.5251619721548294</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J8" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K8" s="81">
+        <f t="shared" si="4"/>
+        <v>0.55527078014578013</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="B9" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D9:I9)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D9:I9),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -6996,17 +7092,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H9" s="81">
-        <f t="shared" si="0"/>
-        <v>0.57557566746611688</v>
+        <f t="shared" si="3"/>
+        <v>0.5864486485987358</v>
       </c>
       <c r="I9" s="81">
-        <f t="shared" si="3"/>
-        <v>0.57557566746611688</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J9" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K9" s="81">
+        <f t="shared" si="4"/>
+        <v>0.61358704414822318</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="B10" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D10:I10)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D10:I10),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -7033,17 +7137,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H10" s="81">
-        <f t="shared" si="0"/>
-        <v>0.52589691994670607</v>
+        <f t="shared" si="3"/>
+        <v>0.51070467769061068</v>
       </c>
       <c r="I10" s="81">
-        <f t="shared" si="3"/>
-        <v>0.52589691994670607</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J10" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K10" s="81">
+        <f t="shared" si="4"/>
+        <v>0.55467506677523692</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="B11" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D11:I11)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D11:I11),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -7070,17 +7182,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H11" s="81">
-        <f t="shared" si="0"/>
-        <v>0.55643026112613903</v>
+        <f t="shared" si="3"/>
+        <v>0.56227504925494742</v>
       </c>
       <c r="I11" s="81">
-        <f t="shared" si="3"/>
-        <v>0.55643026112613903</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J11" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K11" s="81">
+        <f t="shared" si="4"/>
+        <v>0.59478535576972102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="B12" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D12:I12)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D12:I12),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -7107,17 +7227,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H12" s="81">
-        <f t="shared" si="0"/>
-        <v>0.55411627681039211</v>
+        <f t="shared" si="3"/>
+        <v>0.53633855198364799</v>
       </c>
       <c r="I12" s="81">
-        <f t="shared" si="3"/>
-        <v>0.55411627681039211</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J12" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K12" s="81">
+        <f t="shared" si="4"/>
+        <v>0.57461252455871037</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="B13" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D13:I13)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D13:I13),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -7144,17 +7272,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H13" s="81">
-        <f t="shared" si="0"/>
-        <v>0.58964528515813419</v>
+        <f t="shared" si="3"/>
+        <v>0.58874463336286076</v>
       </c>
       <c r="I13" s="81">
-        <f t="shared" si="3"/>
-        <v>0.58964528515813419</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J13" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K13" s="81">
+        <f t="shared" si="4"/>
+        <v>0.61537281007587585</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="B14" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D14:I14)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D14:I14),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -7181,17 +7317,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H14" s="81">
-        <f t="shared" si="0"/>
-        <v>0.49573290598290598</v>
+        <f t="shared" si="3"/>
+        <v>0.46024880212380209</v>
       </c>
       <c r="I14" s="81">
-        <f t="shared" si="3"/>
-        <v>0.49573290598290598</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J14" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K14" s="81">
+        <f t="shared" si="4"/>
+        <v>0.51543160800105248</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="B15" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D15:I15)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D15:I15),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -7218,17 +7362,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H15" s="81">
-        <f t="shared" si="0"/>
-        <v>0.58458190773722951</v>
+        <f t="shared" si="3"/>
+        <v>0.57812004989234178</v>
       </c>
       <c r="I15" s="81">
-        <f t="shared" si="3"/>
-        <v>0.58458190773722951</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J15" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K15" s="81">
+        <f t="shared" si="4"/>
+        <v>0.60710924515436104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="B16" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D16:I16)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D16:I16),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -7255,17 +7407,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H16" s="81">
-        <f t="shared" si="0"/>
-        <v>0.60191439116439127</v>
+        <f t="shared" si="3"/>
+        <v>0.63445246882746875</v>
       </c>
       <c r="I16" s="81">
-        <f t="shared" si="3"/>
-        <v>0.60191439116439127</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J16" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K16" s="81">
+        <f t="shared" si="4"/>
+        <v>0.6509233487705709</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="B17" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D17:I17)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D17:I17),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -7292,17 +7452,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H17" s="81">
-        <f t="shared" si="0"/>
-        <v>0.57487901824529319</v>
+        <f t="shared" si="3"/>
+        <v>0.5821405730556507</v>
       </c>
       <c r="I17" s="81">
-        <f t="shared" si="3"/>
-        <v>0.57487901824529319</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J17" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K17" s="81">
+        <f t="shared" si="4"/>
+        <v>0.61023631872582351</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="B18" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D18:I18)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D18:I18),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -7329,17 +7497,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H18" s="81">
-        <f t="shared" si="0"/>
-        <v>0.57487901824529319</v>
+        <f t="shared" si="3"/>
+        <v>0.5821405730556507</v>
       </c>
       <c r="I18" s="81">
-        <f t="shared" si="3"/>
-        <v>0.57487901824529319</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J18" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K18" s="81">
+        <f t="shared" si="4"/>
+        <v>0.61023631872582351</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="B19" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D19:I19)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D19:I19),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -7366,17 +7542,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H19" s="81">
-        <f t="shared" si="0"/>
-        <v>0.58013438187303579</v>
+        <f t="shared" si="3"/>
+        <v>0.59216963280184454</v>
       </c>
       <c r="I19" s="81">
-        <f t="shared" si="3"/>
-        <v>0.58013438187303579</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J19" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K19" s="81">
+        <f t="shared" si="4"/>
+        <v>0.61803669852841869</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B20" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D20:I20)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D20:I20),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -7403,17 +7587,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H20" s="81">
-        <f t="shared" si="0"/>
-        <v>0.58013438187303579</v>
+        <f t="shared" si="3"/>
+        <v>0.59216963280184454</v>
       </c>
       <c r="I20" s="81">
-        <f t="shared" si="3"/>
-        <v>0.58013438187303579</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J20" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K20" s="81">
+        <f t="shared" si="4"/>
+        <v>0.61803669852841869</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="B21" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D21:I21)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D21:I21),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -7440,17 +7632,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H21" s="81">
-        <f t="shared" si="0"/>
-        <v>0.57487901824529319</v>
+        <f t="shared" si="3"/>
+        <v>0.5821405730556507</v>
       </c>
       <c r="I21" s="81">
-        <f t="shared" si="3"/>
-        <v>0.57487901824529319</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J21" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K21" s="81">
+        <f t="shared" si="4"/>
+        <v>0.61023631872582351</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B22" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D22:I22)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D22:I22),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -7477,17 +7677,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H22" s="81">
-        <f t="shared" si="0"/>
-        <v>0.57487901824529319</v>
+        <f t="shared" si="3"/>
+        <v>0.5821405730556507</v>
       </c>
       <c r="I22" s="81">
-        <f t="shared" si="3"/>
-        <v>0.57487901824529319</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J22" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K22" s="81">
+        <f t="shared" si="4"/>
+        <v>0.61023631872582351</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="B23" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D23:I23)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D23:I23),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -7514,17 +7722,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H23" s="81">
-        <f t="shared" si="0"/>
-        <v>0.57487901824529319</v>
+        <f t="shared" si="3"/>
+        <v>0.5821405730556507</v>
       </c>
       <c r="I23" s="81">
-        <f t="shared" si="3"/>
-        <v>0.57487901824529319</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J23" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K23" s="81">
+        <f t="shared" si="4"/>
+        <v>0.61023631872582351</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="B24" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D24:I24)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D24:I24),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -7551,17 +7767,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H24" s="81">
-        <f t="shared" si="0"/>
-        <v>0.5732623635641757</v>
+        <f t="shared" si="3"/>
+        <v>0.57509219870122874</v>
       </c>
       <c r="I24" s="81">
-        <f t="shared" si="3"/>
-        <v>0.5732623635641757</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J24" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K24" s="81">
+        <f t="shared" si="4"/>
+        <v>0.60475424978349546</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="B25" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D25:I25)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D25:I25),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -7588,17 +7812,25 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H25" s="81">
-        <f t="shared" si="0"/>
-        <v>0.5732623635641757</v>
+        <f t="shared" si="3"/>
+        <v>0.57509219870122874</v>
       </c>
       <c r="I25" s="81">
-        <f t="shared" si="3"/>
-        <v>0.5732623635641757</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J25" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K25" s="81">
+        <f t="shared" si="4"/>
+        <v>0.60475424978349546</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="B26" s="80">
         <f>IFERROR(SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Mapping!D26:I26)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Mapping!D26:I26),SUMPRODUCT(Efficiencies!$C$25:$H$25,Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27)/SUMPRODUCT(Efficiencies!$C$33:$H$33,Efficiencies!$C$27:$H$27))</f>
@@ -7625,11 +7857,19 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H26" s="81">
-        <f t="shared" si="0"/>
-        <v>0.5732623635641757</v>
-      </c>
-      <c r="I26" s="85">
-        <f>I2</f>
+        <f t="shared" si="3"/>
+        <v>0.57509219870122874</v>
+      </c>
+      <c r="I26" s="81">
+        <f>'Low Temp Heat'!$A$122</f>
+        <v>0.76714285714285713</v>
+      </c>
+      <c r="J26" s="81">
+        <f>(1/About!$A$54-1)/(1/About!$A$54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="K26" s="85">
+        <f>K2</f>
         <v>0.57060049240377109</v>
       </c>
     </row>
@@ -7646,7 +7886,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:I26">
+  <conditionalFormatting sqref="B4:H4 B6:H25 B26:G26 K26 B5:G5 K5 B2:G3 K2:K3 H2:H26">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -7686,17 +7926,17 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="19" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="21" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
@@ -7725,35 +7965,35 @@
     <row r="9" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="25"/>
       <c r="B9" s="26" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="D9" s="26"/>
       <c r="E9" s="26" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F9" s="26" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="I9" s="27"/>
       <c r="J9" s="26" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="25" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
@@ -7773,10 +8013,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="D11" s="26" t="s">
         <v>10</v>
@@ -7788,16 +8028,16 @@
         <v>12</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="I11" s="26" t="s">
         <v>13</v>
       </c>
       <c r="J11" s="26" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="28" customFormat="1" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -7820,10 +8060,10 @@
         <v>18</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="I12" s="26" t="s">
         <v>19</v>
@@ -8059,7 +8299,7 @@
         <v>3268</v>
       </c>
       <c r="H23" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="I23" s="41">
         <v>243</v>
@@ -8218,7 +8458,7 @@
         <v>263</v>
       </c>
       <c r="H28" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="I28" s="41">
         <v>46</v>
@@ -8250,7 +8490,7 @@
         <v>481</v>
       </c>
       <c r="H29" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="I29" s="41">
         <v>1</v>
@@ -8281,7 +8521,7 @@
         <v>386</v>
       </c>
       <c r="H30" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="I30" s="41" t="s">
         <v>33</v>
@@ -25067,10 +25307,10 @@
     </row>
     <row r="654" spans="1:10" s="28" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A654" s="38" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B654" s="38" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C654" s="45"/>
       <c r="D654" s="45"/>
@@ -25659,10 +25899,10 @@
     </row>
     <row r="676" spans="1:10" s="28" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A676" s="38" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B676" s="38" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C676" s="45"/>
       <c r="D676" s="45"/>
@@ -27022,7 +27262,7 @@
         <v>1054</v>
       </c>
       <c r="H727" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="I727" s="41">
         <v>15</v>
@@ -27172,7 +27412,7 @@
         <v>160</v>
       </c>
       <c r="H732" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="I732" s="41">
         <v>8</v>
@@ -27202,7 +27442,7 @@
         <v>71</v>
       </c>
       <c r="H733" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="I733" s="41" t="s">
         <v>33</v>
@@ -27232,7 +27472,7 @@
         <v>57</v>
       </c>
       <c r="H734" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="I734" s="41" t="s">
         <v>33</v>
@@ -27701,7 +27941,7 @@
         <v>33</v>
       </c>
       <c r="G752" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="H752" s="41">
         <v>0</v>
@@ -27761,7 +28001,7 @@
         <v>33</v>
       </c>
       <c r="G754" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="H754" s="41" t="s">
         <v>33</v>
@@ -28619,7 +28859,7 @@
     </row>
     <row r="786" spans="1:10" s="28" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A786" s="38" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="B786" s="38" t="s">
         <v>110</v>
@@ -29803,10 +30043,10 @@
     </row>
     <row r="830" spans="1:10" s="28" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A830" s="38" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B830" s="38" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C830" s="45"/>
       <c r="D830" s="45"/>
@@ -31040,16 +31280,16 @@
         <v>0</v>
       </c>
       <c r="F877" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="G877" s="41">
         <v>418</v>
       </c>
       <c r="H877" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="I877" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J877" s="41">
         <v>186</v>
@@ -31160,16 +31400,16 @@
         <v>0</v>
       </c>
       <c r="F881" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="G881" s="41">
         <v>130</v>
       </c>
       <c r="H881" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="I881" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J881" s="41" t="s">
         <v>27</v>
@@ -31190,7 +31430,7 @@
         <v>0</v>
       </c>
       <c r="F882" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="G882" s="41">
         <v>82</v>
@@ -31199,7 +31439,7 @@
         <v>33</v>
       </c>
       <c r="I882" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J882" s="41" t="s">
         <v>27</v>
@@ -31316,7 +31556,7 @@
         <v>43</v>
       </c>
       <c r="H886" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="I886" s="41">
         <v>0</v>
@@ -32171,10 +32411,10 @@
     </row>
     <row r="918" spans="1:10" s="28" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A918" s="38" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="B918" s="38" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C918" s="45"/>
       <c r="D918" s="45"/>
@@ -33402,13 +33642,13 @@
         <v>33</v>
       </c>
       <c r="D965" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="E965" s="41" t="s">
         <v>33</v>
       </c>
       <c r="F965" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="G965" s="41">
         <v>24</v>
@@ -33417,7 +33657,7 @@
         <v>33</v>
       </c>
       <c r="I965" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J965" s="41" t="s">
         <v>33</v>
@@ -33522,13 +33762,13 @@
         <v>27</v>
       </c>
       <c r="D969" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="E969" s="41" t="s">
         <v>33</v>
       </c>
       <c r="F969" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="G969" s="41">
         <v>22</v>
@@ -33537,7 +33777,7 @@
         <v>33</v>
       </c>
       <c r="I969" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J969" s="41" t="s">
         <v>27</v>
@@ -33558,7 +33798,7 @@
         <v>33</v>
       </c>
       <c r="F970" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="G970" s="41">
         <v>20</v>
@@ -33567,7 +33807,7 @@
         <v>33</v>
       </c>
       <c r="I970" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J970" s="41" t="s">
         <v>27</v>
@@ -33612,7 +33852,7 @@
         <v>27</v>
       </c>
       <c r="D972" s="41" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="E972" s="41">
         <v>0</v>
@@ -36907,10 +37147,10 @@
     </row>
     <row r="1094" spans="1:10" s="28" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1094" s="38" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="B1094" s="38" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C1094" s="45"/>
       <c r="D1094" s="45"/>
@@ -42827,10 +43067,10 @@
     </row>
     <row r="1314" spans="1:10" s="28" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1314" s="38" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="B1314" s="38" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C1314" s="45"/>
       <c r="D1314" s="45"/>
@@ -45787,10 +46027,10 @@
     </row>
     <row r="1424" spans="1:10" s="28" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1424" s="38" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B1424" s="38" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C1424" s="45"/>
       <c r="D1424" s="45"/>
@@ -46971,10 +47211,10 @@
     </row>
     <row r="1468" spans="1:10" s="28" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1468" s="38" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B1468" s="38" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C1468" s="45"/>
       <c r="D1468" s="45"/>
@@ -48747,10 +48987,10 @@
     </row>
     <row r="1534" spans="1:10" s="28" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1534" s="47" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B1534" s="38" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C1534" s="45"/>
       <c r="D1534" s="45"/>
@@ -53483,7 +53723,7 @@
     </row>
     <row r="1710" spans="1:10" s="28" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1710" s="47" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="B1710" s="47" t="s">
         <v>179</v>
@@ -57022,296 +57262,296 @@
       </c>
     </row>
     <row r="1841" spans="1:12" s="52" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1841" s="90"/>
-      <c r="B1841" s="90"/>
-      <c r="C1841" s="90"/>
-      <c r="D1841" s="90"/>
-      <c r="E1841" s="90"/>
-      <c r="F1841" s="90"/>
-      <c r="G1841" s="90"/>
-      <c r="H1841" s="90"/>
-      <c r="I1841" s="90"/>
-      <c r="J1841" s="90"/>
+      <c r="A1841" s="89"/>
+      <c r="B1841" s="89"/>
+      <c r="C1841" s="89"/>
+      <c r="D1841" s="89"/>
+      <c r="E1841" s="89"/>
+      <c r="F1841" s="89"/>
+      <c r="G1841" s="89"/>
+      <c r="H1841" s="89"/>
+      <c r="I1841" s="89"/>
+      <c r="J1841" s="89"/>
       <c r="K1841" s="50"/>
       <c r="L1841" s="51"/>
     </row>
     <row r="1842" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1842" s="91"/>
-      <c r="B1842" s="91"/>
-      <c r="C1842" s="91"/>
-      <c r="D1842" s="91"/>
-      <c r="E1842" s="91"/>
-      <c r="F1842" s="91"/>
-      <c r="G1842" s="91"/>
-      <c r="H1842" s="91"/>
-      <c r="I1842" s="91"/>
-      <c r="J1842" s="91"/>
+      <c r="A1842" s="90"/>
+      <c r="B1842" s="90"/>
+      <c r="C1842" s="90"/>
+      <c r="D1842" s="90"/>
+      <c r="E1842" s="90"/>
+      <c r="F1842" s="90"/>
+      <c r="G1842" s="90"/>
+      <c r="H1842" s="90"/>
+      <c r="I1842" s="90"/>
+      <c r="J1842" s="90"/>
       <c r="K1842" s="53"/>
       <c r="L1842" s="54"/>
     </row>
     <row r="1843" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1843" s="91"/>
-      <c r="B1843" s="91"/>
-      <c r="C1843" s="91"/>
-      <c r="D1843" s="91"/>
-      <c r="E1843" s="91"/>
-      <c r="F1843" s="91"/>
-      <c r="G1843" s="91"/>
-      <c r="H1843" s="91"/>
-      <c r="I1843" s="91"/>
-      <c r="J1843" s="91"/>
+      <c r="A1843" s="90"/>
+      <c r="B1843" s="90"/>
+      <c r="C1843" s="90"/>
+      <c r="D1843" s="90"/>
+      <c r="E1843" s="90"/>
+      <c r="F1843" s="90"/>
+      <c r="G1843" s="90"/>
+      <c r="H1843" s="90"/>
+      <c r="I1843" s="90"/>
+      <c r="J1843" s="90"/>
       <c r="K1843" s="53"/>
       <c r="L1843" s="54"/>
     </row>
     <row r="1844" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1844" s="89"/>
-      <c r="B1844" s="89"/>
-      <c r="C1844" s="89"/>
-      <c r="D1844" s="89"/>
-      <c r="E1844" s="89"/>
-      <c r="F1844" s="89"/>
-      <c r="G1844" s="89"/>
-      <c r="H1844" s="89"/>
-      <c r="I1844" s="89"/>
-      <c r="J1844" s="89"/>
+      <c r="A1844" s="88"/>
+      <c r="B1844" s="88"/>
+      <c r="C1844" s="88"/>
+      <c r="D1844" s="88"/>
+      <c r="E1844" s="88"/>
+      <c r="F1844" s="88"/>
+      <c r="G1844" s="88"/>
+      <c r="H1844" s="88"/>
+      <c r="I1844" s="88"/>
+      <c r="J1844" s="88"/>
       <c r="K1844" s="55"/>
       <c r="L1844" s="54"/>
     </row>
     <row r="1845" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1845" s="89"/>
-      <c r="B1845" s="89"/>
-      <c r="C1845" s="89"/>
-      <c r="D1845" s="89"/>
-      <c r="E1845" s="89"/>
-      <c r="F1845" s="89"/>
-      <c r="G1845" s="89"/>
-      <c r="H1845" s="89"/>
-      <c r="I1845" s="89"/>
-      <c r="J1845" s="89"/>
+      <c r="A1845" s="88"/>
+      <c r="B1845" s="88"/>
+      <c r="C1845" s="88"/>
+      <c r="D1845" s="88"/>
+      <c r="E1845" s="88"/>
+      <c r="F1845" s="88"/>
+      <c r="G1845" s="88"/>
+      <c r="H1845" s="88"/>
+      <c r="I1845" s="88"/>
+      <c r="J1845" s="88"/>
       <c r="K1845" s="55"/>
       <c r="L1845" s="54"/>
     </row>
     <row r="1846" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1846" s="89"/>
-      <c r="B1846" s="89"/>
-      <c r="C1846" s="89"/>
-      <c r="D1846" s="89"/>
-      <c r="E1846" s="89"/>
-      <c r="F1846" s="89"/>
-      <c r="G1846" s="89"/>
-      <c r="H1846" s="89"/>
-      <c r="I1846" s="89"/>
-      <c r="J1846" s="89"/>
+      <c r="A1846" s="88"/>
+      <c r="B1846" s="88"/>
+      <c r="C1846" s="88"/>
+      <c r="D1846" s="88"/>
+      <c r="E1846" s="88"/>
+      <c r="F1846" s="88"/>
+      <c r="G1846" s="88"/>
+      <c r="H1846" s="88"/>
+      <c r="I1846" s="88"/>
+      <c r="J1846" s="88"/>
       <c r="K1846" s="55"/>
       <c r="L1846" s="54"/>
     </row>
     <row r="1847" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1847" s="89"/>
-      <c r="B1847" s="89"/>
-      <c r="C1847" s="89"/>
-      <c r="D1847" s="89"/>
-      <c r="E1847" s="89"/>
-      <c r="F1847" s="89"/>
-      <c r="G1847" s="89"/>
-      <c r="H1847" s="89"/>
-      <c r="I1847" s="89"/>
-      <c r="J1847" s="89"/>
+      <c r="A1847" s="88"/>
+      <c r="B1847" s="88"/>
+      <c r="C1847" s="88"/>
+      <c r="D1847" s="88"/>
+      <c r="E1847" s="88"/>
+      <c r="F1847" s="88"/>
+      <c r="G1847" s="88"/>
+      <c r="H1847" s="88"/>
+      <c r="I1847" s="88"/>
+      <c r="J1847" s="88"/>
       <c r="K1847" s="55"/>
       <c r="L1847" s="54"/>
     </row>
     <row r="1848" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1848" s="88"/>
-      <c r="B1848" s="88"/>
-      <c r="C1848" s="88"/>
-      <c r="D1848" s="88"/>
-      <c r="E1848" s="88"/>
-      <c r="F1848" s="88"/>
-      <c r="G1848" s="88"/>
-      <c r="H1848" s="88"/>
-      <c r="I1848" s="88"/>
-      <c r="J1848" s="88"/>
+      <c r="A1848" s="91"/>
+      <c r="B1848" s="91"/>
+      <c r="C1848" s="91"/>
+      <c r="D1848" s="91"/>
+      <c r="E1848" s="91"/>
+      <c r="F1848" s="91"/>
+      <c r="G1848" s="91"/>
+      <c r="H1848" s="91"/>
+      <c r="I1848" s="91"/>
+      <c r="J1848" s="91"/>
       <c r="K1848" s="54"/>
       <c r="L1848" s="54"/>
     </row>
     <row r="1849" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1849" s="88"/>
-      <c r="B1849" s="88"/>
-      <c r="C1849" s="88"/>
-      <c r="D1849" s="88"/>
-      <c r="E1849" s="88"/>
-      <c r="F1849" s="88"/>
-      <c r="G1849" s="88"/>
-      <c r="H1849" s="88"/>
-      <c r="I1849" s="88"/>
-      <c r="J1849" s="88"/>
+      <c r="A1849" s="91"/>
+      <c r="B1849" s="91"/>
+      <c r="C1849" s="91"/>
+      <c r="D1849" s="91"/>
+      <c r="E1849" s="91"/>
+      <c r="F1849" s="91"/>
+      <c r="G1849" s="91"/>
+      <c r="H1849" s="91"/>
+      <c r="I1849" s="91"/>
+      <c r="J1849" s="91"/>
       <c r="K1849" s="54"/>
       <c r="L1849" s="54"/>
     </row>
     <row r="1850" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1850" s="89"/>
-      <c r="B1850" s="89"/>
-      <c r="C1850" s="89"/>
-      <c r="D1850" s="89"/>
-      <c r="E1850" s="89"/>
-      <c r="F1850" s="89"/>
-      <c r="G1850" s="89"/>
-      <c r="H1850" s="89"/>
-      <c r="I1850" s="89"/>
-      <c r="J1850" s="89"/>
+      <c r="A1850" s="88"/>
+      <c r="B1850" s="88"/>
+      <c r="C1850" s="88"/>
+      <c r="D1850" s="88"/>
+      <c r="E1850" s="88"/>
+      <c r="F1850" s="88"/>
+      <c r="G1850" s="88"/>
+      <c r="H1850" s="88"/>
+      <c r="I1850" s="88"/>
+      <c r="J1850" s="88"/>
       <c r="K1850" s="55"/>
       <c r="L1850" s="54"/>
     </row>
     <row r="1851" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1851" s="89"/>
-      <c r="B1851" s="89"/>
-      <c r="C1851" s="89"/>
-      <c r="D1851" s="89"/>
-      <c r="E1851" s="89"/>
-      <c r="F1851" s="89"/>
-      <c r="G1851" s="89"/>
-      <c r="H1851" s="89"/>
-      <c r="I1851" s="89"/>
-      <c r="J1851" s="89"/>
+      <c r="A1851" s="88"/>
+      <c r="B1851" s="88"/>
+      <c r="C1851" s="88"/>
+      <c r="D1851" s="88"/>
+      <c r="E1851" s="88"/>
+      <c r="F1851" s="88"/>
+      <c r="G1851" s="88"/>
+      <c r="H1851" s="88"/>
+      <c r="I1851" s="88"/>
+      <c r="J1851" s="88"/>
       <c r="K1851" s="55"/>
       <c r="L1851" s="54"/>
     </row>
     <row r="1852" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1852" s="89"/>
-      <c r="B1852" s="89"/>
-      <c r="C1852" s="89"/>
-      <c r="D1852" s="89"/>
-      <c r="E1852" s="89"/>
-      <c r="F1852" s="89"/>
-      <c r="G1852" s="89"/>
-      <c r="H1852" s="89"/>
-      <c r="I1852" s="89"/>
-      <c r="J1852" s="89"/>
+      <c r="A1852" s="88"/>
+      <c r="B1852" s="88"/>
+      <c r="C1852" s="88"/>
+      <c r="D1852" s="88"/>
+      <c r="E1852" s="88"/>
+      <c r="F1852" s="88"/>
+      <c r="G1852" s="88"/>
+      <c r="H1852" s="88"/>
+      <c r="I1852" s="88"/>
+      <c r="J1852" s="88"/>
       <c r="K1852" s="55"/>
       <c r="L1852" s="54"/>
     </row>
     <row r="1853" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1853" s="89"/>
-      <c r="B1853" s="89"/>
-      <c r="C1853" s="89"/>
-      <c r="D1853" s="89"/>
-      <c r="E1853" s="89"/>
-      <c r="F1853" s="89"/>
-      <c r="G1853" s="89"/>
-      <c r="H1853" s="89"/>
-      <c r="I1853" s="89"/>
-      <c r="J1853" s="89"/>
+      <c r="A1853" s="88"/>
+      <c r="B1853" s="88"/>
+      <c r="C1853" s="88"/>
+      <c r="D1853" s="88"/>
+      <c r="E1853" s="88"/>
+      <c r="F1853" s="88"/>
+      <c r="G1853" s="88"/>
+      <c r="H1853" s="88"/>
+      <c r="I1853" s="88"/>
+      <c r="J1853" s="88"/>
       <c r="K1853" s="55"/>
       <c r="L1853" s="54"/>
     </row>
     <row r="1854" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1854" s="89"/>
-      <c r="B1854" s="89"/>
-      <c r="C1854" s="89"/>
-      <c r="D1854" s="89"/>
-      <c r="E1854" s="89"/>
-      <c r="F1854" s="89"/>
-      <c r="G1854" s="89"/>
-      <c r="H1854" s="89"/>
-      <c r="I1854" s="89"/>
-      <c r="J1854" s="89"/>
+      <c r="A1854" s="88"/>
+      <c r="B1854" s="88"/>
+      <c r="C1854" s="88"/>
+      <c r="D1854" s="88"/>
+      <c r="E1854" s="88"/>
+      <c r="F1854" s="88"/>
+      <c r="G1854" s="88"/>
+      <c r="H1854" s="88"/>
+      <c r="I1854" s="88"/>
+      <c r="J1854" s="88"/>
       <c r="K1854" s="55"/>
       <c r="L1854" s="54"/>
     </row>
     <row r="1855" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1855" s="89"/>
-      <c r="B1855" s="89"/>
-      <c r="C1855" s="89"/>
-      <c r="D1855" s="89"/>
-      <c r="E1855" s="89"/>
-      <c r="F1855" s="89"/>
-      <c r="G1855" s="89"/>
-      <c r="H1855" s="89"/>
-      <c r="I1855" s="89"/>
-      <c r="J1855" s="89"/>
+      <c r="A1855" s="88"/>
+      <c r="B1855" s="88"/>
+      <c r="C1855" s="88"/>
+      <c r="D1855" s="88"/>
+      <c r="E1855" s="88"/>
+      <c r="F1855" s="88"/>
+      <c r="G1855" s="88"/>
+      <c r="H1855" s="88"/>
+      <c r="I1855" s="88"/>
+      <c r="J1855" s="88"/>
       <c r="K1855" s="55"/>
       <c r="L1855" s="54"/>
     </row>
     <row r="1856" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1856" s="88"/>
-      <c r="B1856" s="88"/>
-      <c r="C1856" s="88"/>
-      <c r="D1856" s="88"/>
-      <c r="E1856" s="88"/>
-      <c r="F1856" s="88"/>
-      <c r="G1856" s="88"/>
-      <c r="H1856" s="88"/>
-      <c r="I1856" s="88"/>
-      <c r="J1856" s="88"/>
+      <c r="A1856" s="91"/>
+      <c r="B1856" s="91"/>
+      <c r="C1856" s="91"/>
+      <c r="D1856" s="91"/>
+      <c r="E1856" s="91"/>
+      <c r="F1856" s="91"/>
+      <c r="G1856" s="91"/>
+      <c r="H1856" s="91"/>
+      <c r="I1856" s="91"/>
+      <c r="J1856" s="91"/>
       <c r="K1856" s="54"/>
       <c r="L1856" s="54"/>
     </row>
     <row r="1857" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1857" s="88"/>
-      <c r="B1857" s="88"/>
-      <c r="C1857" s="88"/>
-      <c r="D1857" s="88"/>
-      <c r="E1857" s="88"/>
-      <c r="F1857" s="88"/>
-      <c r="G1857" s="88"/>
-      <c r="H1857" s="88"/>
-      <c r="I1857" s="88"/>
-      <c r="J1857" s="88"/>
+      <c r="A1857" s="91"/>
+      <c r="B1857" s="91"/>
+      <c r="C1857" s="91"/>
+      <c r="D1857" s="91"/>
+      <c r="E1857" s="91"/>
+      <c r="F1857" s="91"/>
+      <c r="G1857" s="91"/>
+      <c r="H1857" s="91"/>
+      <c r="I1857" s="91"/>
+      <c r="J1857" s="91"/>
       <c r="K1857" s="54"/>
       <c r="L1857" s="54"/>
     </row>
     <row r="1858" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1858" s="88"/>
-      <c r="B1858" s="88"/>
-      <c r="C1858" s="88"/>
-      <c r="D1858" s="88"/>
-      <c r="E1858" s="88"/>
-      <c r="F1858" s="88"/>
-      <c r="G1858" s="88"/>
-      <c r="H1858" s="88"/>
-      <c r="I1858" s="88"/>
-      <c r="J1858" s="88"/>
+      <c r="A1858" s="91"/>
+      <c r="B1858" s="91"/>
+      <c r="C1858" s="91"/>
+      <c r="D1858" s="91"/>
+      <c r="E1858" s="91"/>
+      <c r="F1858" s="91"/>
+      <c r="G1858" s="91"/>
+      <c r="H1858" s="91"/>
+      <c r="I1858" s="91"/>
+      <c r="J1858" s="91"/>
       <c r="K1858" s="54"/>
       <c r="L1858" s="54"/>
     </row>
     <row r="1859" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1859" s="88"/>
-      <c r="B1859" s="88"/>
-      <c r="C1859" s="88"/>
-      <c r="D1859" s="88"/>
-      <c r="E1859" s="88"/>
-      <c r="F1859" s="88"/>
-      <c r="G1859" s="88"/>
-      <c r="H1859" s="88"/>
-      <c r="I1859" s="88"/>
-      <c r="J1859" s="88"/>
+      <c r="A1859" s="91"/>
+      <c r="B1859" s="91"/>
+      <c r="C1859" s="91"/>
+      <c r="D1859" s="91"/>
+      <c r="E1859" s="91"/>
+      <c r="F1859" s="91"/>
+      <c r="G1859" s="91"/>
+      <c r="H1859" s="91"/>
+      <c r="I1859" s="91"/>
+      <c r="J1859" s="91"/>
       <c r="K1859" s="54"/>
       <c r="L1859" s="54"/>
     </row>
     <row r="1860" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1860" s="89"/>
-      <c r="B1860" s="89"/>
-      <c r="C1860" s="89"/>
-      <c r="D1860" s="89"/>
-      <c r="E1860" s="89"/>
-      <c r="F1860" s="89"/>
-      <c r="G1860" s="89"/>
-      <c r="H1860" s="89"/>
-      <c r="I1860" s="89"/>
-      <c r="J1860" s="89"/>
+      <c r="A1860" s="88"/>
+      <c r="B1860" s="88"/>
+      <c r="C1860" s="88"/>
+      <c r="D1860" s="88"/>
+      <c r="E1860" s="88"/>
+      <c r="F1860" s="88"/>
+      <c r="G1860" s="88"/>
+      <c r="H1860" s="88"/>
+      <c r="I1860" s="88"/>
+      <c r="J1860" s="88"/>
       <c r="K1860" s="55"/>
       <c r="L1860" s="54"/>
     </row>
     <row r="1861" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1861" s="88"/>
-      <c r="B1861" s="88"/>
-      <c r="C1861" s="88"/>
-      <c r="D1861" s="88"/>
-      <c r="E1861" s="88"/>
-      <c r="F1861" s="88"/>
-      <c r="G1861" s="88"/>
-      <c r="H1861" s="88"/>
-      <c r="I1861" s="88"/>
-      <c r="J1861" s="88"/>
+      <c r="A1861" s="91"/>
+      <c r="B1861" s="91"/>
+      <c r="C1861" s="91"/>
+      <c r="D1861" s="91"/>
+      <c r="E1861" s="91"/>
+      <c r="F1861" s="91"/>
+      <c r="G1861" s="91"/>
+      <c r="H1861" s="91"/>
+      <c r="I1861" s="91"/>
+      <c r="J1861" s="91"/>
       <c r="K1861" s="54"/>
     </row>
     <row r="1862" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
@@ -57387,6 +57627,15 @@
     <row r="1880" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1859:J1859"/>
+    <mergeCell ref="A1860:J1860"/>
+    <mergeCell ref="A1861:J1861"/>
+    <mergeCell ref="A1853:J1853"/>
+    <mergeCell ref="A1854:J1854"/>
+    <mergeCell ref="A1855:J1855"/>
+    <mergeCell ref="A1856:J1856"/>
+    <mergeCell ref="A1857:J1857"/>
+    <mergeCell ref="A1858:J1858"/>
     <mergeCell ref="A1852:J1852"/>
     <mergeCell ref="A1841:J1841"/>
     <mergeCell ref="A1842:J1842"/>
@@ -57399,15 +57648,6 @@
     <mergeCell ref="A1849:J1849"/>
     <mergeCell ref="A1850:J1850"/>
     <mergeCell ref="A1851:J1851"/>
-    <mergeCell ref="A1859:J1859"/>
-    <mergeCell ref="A1860:J1860"/>
-    <mergeCell ref="A1861:J1861"/>
-    <mergeCell ref="A1853:J1853"/>
-    <mergeCell ref="A1854:J1854"/>
-    <mergeCell ref="A1855:J1855"/>
-    <mergeCell ref="A1856:J1856"/>
-    <mergeCell ref="A1857:J1857"/>
-    <mergeCell ref="A1858:J1858"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="95" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -57623,7 +57863,7 @@
         <v>0.91416443955352933</v>
       </c>
       <c r="B36" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -57655,7 +57895,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E954BD9-F2E9-49BD-A674-73E808A9938A}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:J122"/>
+  <dimension ref="A1:J126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -58224,7 +58464,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -58233,7 +58473,7 @@
         <v>3.5</v>
       </c>
       <c r="B101" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -58242,7 +58482,7 @@
         <v>2.1</v>
       </c>
       <c r="B102" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -58251,7 +58491,7 @@
         <v>0.556552087560372</v>
       </c>
       <c r="B104" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -58260,7 +58500,7 @@
         <v>0.44344791243962806</v>
       </c>
       <c r="B105" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -58269,77 +58509,106 @@
         <v>2.8791729225845208</v>
       </c>
       <c r="B107" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A109" s="4">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" s="4">
+        <f>A101</f>
+        <v>3.5</v>
+      </c>
+      <c r="B108" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" s="4">
         <f>Efficiencies!E4</f>
         <v>0.71</v>
       </c>
-      <c r="B109" t="s">
-        <v>425</v>
+      <c r="B110" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="A111" s="4">
+        <f>A83</f>
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="B111" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112">
-        <f>1/A109</f>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <f>1/A110</f>
         <v>1.4084507042253522</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B114" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A115">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117">
         <f>1/A107</f>
         <v>0.34732196602569432</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B117" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A118" s="17">
-        <f>(A112-A115)/A112</f>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" s="17">
+        <f>(A114-A117)/A114</f>
         <v>0.75340140412175705</v>
       </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A120" s="75"/>
-      <c r="B120" s="75"/>
-      <c r="C120" s="75"/>
-      <c r="D120" s="75"/>
-      <c r="E120" s="75"/>
-      <c r="F120" s="75"/>
-      <c r="G120" s="75"/>
-      <c r="H120" s="75"/>
-      <c r="I120" s="75"/>
-      <c r="J120" s="75"/>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>426</v>
+        <v>552</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A122" s="76">
-        <f>AVERAGE(A95,A118)</f>
+      <c r="A122" s="7">
+        <f>(1/A111-1/A108)/(1/A111)</f>
+        <v>0.76714285714285713</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" s="75"/>
+      <c r="B124" s="75"/>
+      <c r="C124" s="75"/>
+      <c r="D124" s="75"/>
+      <c r="E124" s="75"/>
+      <c r="F124" s="75"/>
+      <c r="G124" s="75"/>
+      <c r="H124" s="75"/>
+      <c r="I124" s="75"/>
+      <c r="J124" s="75"/>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" s="76">
+        <f>AVERAGE(A95,A120)</f>
         <v>0.71370070206087854</v>
       </c>
     </row>
@@ -58362,7 +58631,7 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -58372,18 +58641,18 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="B3" s="58" t="s">
         <v>231</v>
       </c>
       <c r="C3" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="B4" s="79">
         <v>4.95</v>
@@ -58395,7 +58664,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="B5" s="79">
         <v>1.0129999999999999</v>
@@ -58407,7 +58676,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -58417,18 +58686,18 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="B8" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C8" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="B9">
         <v>6.5</v>
@@ -58440,7 +58709,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="58" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="B10">
         <v>1.2</v>
@@ -58452,7 +58721,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -58462,7 +58731,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="B13" s="6">
         <f>(C5-C4)/C5</f>
@@ -58471,7 +58740,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="58" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B14" s="6">
         <f>(C10-C9)/C10</f>
@@ -58480,7 +58749,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="B15" s="10">
         <f>AVERAGE(B13:B14)</f>
@@ -58507,7 +58776,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="86" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="B1" s="86"/>
       <c r="C1" s="86"/>
@@ -58527,7 +58796,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -58537,30 +58806,30 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="C3" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="D3" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="E3" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="F3" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="H3" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="82" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B4" s="87">
         <v>0.30299999999999999</v>
@@ -58579,12 +58848,12 @@
         <v>19</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="B5" s="87">
         <f>AVERAGE(0.35,0.305,0.266)</f>
@@ -58595,7 +58864,7 @@
         <v>3.2573289902280131</v>
       </c>
       <c r="D5" s="79" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="E5">
         <v>2100</v>
@@ -58606,7 +58875,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -58616,18 +58885,18 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="C8" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="B9">
         <f>AVERAGE(0.836,0.885,0.905)</f>
@@ -58638,7 +58907,7 @@
         <v>1.1424219345011424</v>
       </c>
       <c r="D9" s="79" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="E9">
         <v>2600</v>
@@ -58649,7 +58918,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="82" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="B10">
         <f>B9*(1-AVERAGE(0.1,0.15))</f>
@@ -58661,12 +58930,12 @@
       </c>
       <c r="D10" s="79"/>
       <c r="F10" s="79" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="B11">
         <f>1/C11</f>
@@ -58685,7 +58954,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="58" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="B12">
         <f>1/C12</f>
@@ -58702,7 +58971,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -58712,7 +58981,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="B15" s="6">
         <f>(AVERAGE(C4:C5)-AVERAGE(C10:C12))/AVERAGE(C4:C5)</f>
@@ -58728,104 +58997,104 @@
     </row>
     <row r="19" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H19" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
     </row>
     <row r="20" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H20" s="16" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="D33" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>493</v>
+      </c>
+      <c r="B34" t="s">
+        <v>500</v>
+      </c>
+      <c r="D34" t="s">
+        <v>512</v>
+      </c>
+      <c r="E34" t="s">
+        <v>515</v>
+      </c>
+      <c r="F34" t="s">
+        <v>505</v>
+      </c>
+      <c r="G34" t="s">
+        <v>517</v>
+      </c>
+      <c r="H34" t="s">
+        <v>504</v>
+      </c>
+      <c r="I34" t="s">
+        <v>518</v>
+      </c>
+      <c r="J34" t="s">
+        <v>494</v>
+      </c>
+      <c r="M34" t="s">
         <v>501</v>
       </c>
-      <c r="B34" t="s">
-        <v>508</v>
-      </c>
-      <c r="D34" t="s">
-        <v>520</v>
-      </c>
-      <c r="E34" t="s">
-        <v>523</v>
-      </c>
-      <c r="F34" t="s">
-        <v>513</v>
-      </c>
-      <c r="G34" t="s">
-        <v>525</v>
-      </c>
-      <c r="H34" t="s">
-        <v>512</v>
-      </c>
-      <c r="I34" t="s">
-        <v>526</v>
-      </c>
-      <c r="J34" t="s">
-        <v>502</v>
-      </c>
-      <c r="M34" t="s">
-        <v>509</v>
-      </c>
       <c r="P34" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="S34" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="T34" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>488</v>
+      </c>
+      <c r="B35" t="s">
+        <v>502</v>
+      </c>
+      <c r="C35" t="s">
+        <v>503</v>
+      </c>
+      <c r="J35" t="s">
+        <v>495</v>
+      </c>
+      <c r="K35" t="s">
         <v>496</v>
       </c>
-      <c r="B35" t="s">
-        <v>510</v>
-      </c>
-      <c r="C35" t="s">
-        <v>511</v>
-      </c>
-      <c r="J35" t="s">
-        <v>503</v>
-      </c>
-      <c r="K35" t="s">
-        <v>504</v>
-      </c>
       <c r="L35" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="M35" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="N35" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="O35" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="P35" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="Q35" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="R35" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="B36" s="83">
         <f>AVERAGE(S36:S37)</f>
@@ -58936,7 +59205,7 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="B38" s="83">
         <f>AVERAGE(S38:S40)</f>
@@ -59088,7 +59357,7 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="B41" s="83">
         <f>AVERAGE(S41:S43)</f>
@@ -59228,51 +59497,51 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="57" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="58"/>
       <c r="I1" s="2" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="J1" s="59"/>
       <c r="K1" s="59"/>
     </row>
     <row r="2" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="60" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B2" s="60" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C2" s="61" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D2" s="61" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="E2" s="61" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F2" s="61" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="I2" s="62" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="J2" s="62" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="K2" s="62" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="D3"/>
       <c r="E3" s="63">
@@ -59290,10 +59559,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B4" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="D4"/>
       <c r="E4" s="63">
@@ -59311,10 +59580,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="B5" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="D5"/>
       <c r="E5" s="63">
@@ -59332,10 +59601,10 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B6" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="D6"/>
       <c r="E6" s="63">
@@ -59353,10 +59622,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B7" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C7" s="64">
         <v>0.84</v>
@@ -59383,10 +59652,10 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B8" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C8" s="64">
         <v>0.68</v>
@@ -59413,10 +59682,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="B9" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="D9"/>
       <c r="E9" s="63">
@@ -59438,36 +59707,36 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="57" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="B11" s="6"/>
       <c r="I11" s="2" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="60" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B12" s="60" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E12" s="61" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="G12" s="60" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="I12" s="62" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B13" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E13" s="10">
         <v>0.96</v>
@@ -59486,10 +59755,10 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B14" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="E14" s="10">
         <v>3.5</v>
@@ -59508,10 +59777,10 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="B15" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="E15" s="10">
         <v>2.1</v>
@@ -59530,10 +59799,10 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B16" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="E16" s="10">
         <v>0.99</v>
@@ -59552,10 +59821,10 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B17" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="E17" s="10">
         <v>0.99</v>
@@ -59574,10 +59843,10 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>312</v>
+      </c>
+      <c r="B18" t="s">
         <v>320</v>
-      </c>
-      <c r="B18" t="s">
-        <v>328</v>
       </c>
       <c r="E18" s="10">
         <v>0.99</v>
@@ -59596,10 +59865,10 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>313</v>
+      </c>
+      <c r="B19" t="s">
         <v>321</v>
-      </c>
-      <c r="B19" t="s">
-        <v>329</v>
       </c>
       <c r="E19" s="10">
         <v>0.9</v>
@@ -59651,7 +59920,7 @@
     </row>
     <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="60" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="B24" s="67">
         <f t="array" ref="B24:H24">TRANSPOSE(E3:E9/E13:E19)</f>
@@ -59678,7 +59947,7 @@
     </row>
     <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="60" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="B25" s="78" cm="1">
         <f t="array" ref="B25:H25">TRANSPOSE(G13:G19)</f>
@@ -59709,7 +59978,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C27" s="4">
         <f>AVERAGE('Temperature Breakdown'!D25:D39)</f>
@@ -59742,10 +60011,10 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="B30" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="C30" s="4">
         <v>1</v>
@@ -59760,7 +60029,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="E31" s="4">
         <f>1-E30</f>
@@ -59773,7 +60042,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="F32" s="6">
         <f>150/250</f>
@@ -59788,7 +60057,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C33" s="4">
         <v>1</v>
@@ -59805,10 +60074,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="B35" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="C35" s="6">
         <f>SUMPRODUCT(C30:H30,$C$25:$H$25,$C$27:$H$27)/SUMPRODUCT(C30:H30,$C$27:$H$27)</f>
@@ -59817,7 +60086,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="C36" s="6">
         <f t="shared" ref="C36:C38" si="3">SUMPRODUCT(C31:H31,$C$25:$H$25,$C$27:$H$27)/SUMPRODUCT(C31:H31,$C$27:$H$27)</f>
@@ -59826,7 +60095,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="C37" s="6">
         <f t="shared" si="3"/>
@@ -59835,7 +60104,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C38" s="6">
         <f t="shared" si="3"/>
@@ -59866,7 +60135,7 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="69" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B1" s="69"/>
       <c r="C1" s="69"/>
@@ -59877,20 +60146,20 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D3" s="92" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="E3" s="92"/>
       <c r="F3" s="92"/>
       <c r="G3" s="92"/>
       <c r="I3" s="2" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
@@ -59898,7 +60167,7 @@
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
       <c r="P3" s="2" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
@@ -59908,63 +60177,63 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="R4" s="13" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="S4" s="13" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="T4" s="13" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="U4" s="13" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B5" s="4">
         <v>0.32</v>
@@ -60035,7 +60304,7 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B6" s="4">
         <v>0.28000000000000003</v>
@@ -60106,7 +60375,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B7" s="4">
         <v>0.35</v>
@@ -60177,7 +60446,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="B8" s="4">
         <v>0.18</v>
@@ -60248,7 +60517,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B9" s="4">
         <v>0.28999999999999998</v>
@@ -60319,7 +60588,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="B10" s="4">
         <v>0.21</v>
@@ -60390,7 +60659,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="B11" s="4">
         <v>0.21</v>
@@ -60461,7 +60730,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="B12" s="4">
         <v>0.4</v>
@@ -60532,7 +60801,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="B13" s="4">
         <v>0.09</v>
@@ -60603,7 +60872,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B14" s="4">
         <v>7.0000000000000007E-2</v>
@@ -60674,7 +60943,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="B15" s="4">
         <v>0.34</v>
@@ -60745,7 +61014,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B16" s="4">
         <v>0.23</v>
@@ -60816,7 +61085,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="B17" s="4">
         <v>0.24</v>
@@ -60887,7 +61156,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B18" s="4">
         <v>0.11</v>
@@ -60958,7 +61227,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B19" s="4">
         <v>0.13</v>
@@ -61029,36 +61298,36 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B23" s="72" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="B24" s="65" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="E24" s="66" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="F24" s="66" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G24" s="66" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="H24" s="66" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="I24" s="66" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="K24" s="73" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="L24" s="15" t="s">
         <v>208</v>
@@ -61066,7 +61335,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="B25" s="6">
         <v>5.0078247261345854E-2</v>
@@ -61096,7 +61365,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B26" s="6">
         <v>4.3478260869565216E-2</v>
@@ -61132,7 +61401,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="B27" s="6">
         <v>0.11666666666666667</v>
@@ -61168,7 +61437,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B28" s="6">
         <v>2.4711696869851731E-2</v>
@@ -61198,7 +61467,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B29" s="6">
         <v>3.3707865168539325E-2</v>
@@ -61228,7 +61497,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B30" s="6">
         <v>0.11190576356752209</v>
@@ -61258,7 +61527,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="B31" s="6">
         <v>0</v>
@@ -61288,7 +61557,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B32" s="6">
         <v>0.10199999999999999</v>
@@ -61318,7 +61587,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B33" s="6">
         <v>0.13189448441247004</v>
@@ -61354,7 +61623,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="B34" s="6">
         <v>2.9702970297029702E-2</v>
@@ -61384,7 +61653,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="B35" s="6">
         <v>0.1875</v>
@@ -61420,7 +61689,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="B36" s="6">
         <v>8.1632653061224483E-2</v>
@@ -61456,7 +61725,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B37" s="6">
         <v>7.6923076923076927E-2</v>
@@ -61490,12 +61759,12 @@
         <v>12</v>
       </c>
       <c r="L37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B38" s="6">
         <v>0</v>
@@ -61529,12 +61798,12 @@
         <v>12</v>
       </c>
       <c r="L38" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B39" s="6">
         <v>7.1428571428571425E-2</v>
@@ -61568,12 +61837,12 @@
         <v>12</v>
       </c>
       <c r="L39" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="D40" s="4">
         <f>P10</f>
@@ -61630,22 +61899,22 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="74" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C1" s="71" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -61653,19 +61922,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C2" s="58">
         <v>2024</v>
       </c>
       <c r="D2" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="F2" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -61679,10 +61948,10 @@
         <v>2021</v>
       </c>
       <c r="D3" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="F3" t="s">
         <v>193</v>
@@ -61693,19 +61962,19 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="C4" s="58">
         <v>2024</v>
       </c>
       <c r="D4" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="F4" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -61713,19 +61982,19 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C5" s="58">
         <v>2015</v>
       </c>
       <c r="D5" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="F5" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -61733,19 +62002,19 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C6" s="58">
         <v>2015</v>
       </c>
       <c r="D6" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="F6" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -61753,19 +62022,19 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C7" s="58">
         <v>2023</v>
       </c>
       <c r="D7" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="F7" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -61773,19 +62042,19 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C8" s="58">
         <v>2021</v>
       </c>
       <c r="D8" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="F8" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -61793,19 +62062,19 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C9" s="58">
         <v>2017</v>
       </c>
       <c r="D9" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="F9" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -61813,19 +62082,19 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C10" s="58">
         <v>2006</v>
       </c>
       <c r="D10" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="F10" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -61839,13 +62108,13 @@
         <v>2014</v>
       </c>
       <c r="D11" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="F11" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -61853,16 +62122,16 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="C12" s="58">
         <v>2014</v>
       </c>
       <c r="D12" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -61870,16 +62139,16 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="C13" s="58">
         <v>2016</v>
       </c>
       <c r="D13" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -61887,16 +62156,16 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="C14" s="58">
         <v>2020</v>
       </c>
       <c r="D14" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -61904,16 +62173,16 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="C15" s="58">
         <v>2022</v>
       </c>
       <c r="D15" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -61921,16 +62190,16 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="C16" s="58">
         <v>2021</v>
       </c>
       <c r="D16" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -61938,16 +62207,16 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="C17" s="58">
         <v>2018</v>
       </c>
       <c r="D17" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -61961,10 +62230,10 @@
         <v>2015</v>
       </c>
       <c r="D18" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
